--- a/HR_Employee_Onboarding_Form_Fields_Master_Template.xlsx
+++ b/HR_Employee_Onboarding_Form_Fields_Master_Template.xlsx
@@ -82,7 +82,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -167,8 +167,20 @@
         <bgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F8FF"/>
+        <bgColor rgb="00F0F8FF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -190,11 +202,25 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -261,6 +287,24 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -627,8 +671,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K95"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -4561,217 +4605,1047 @@
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="22" t="inlineStr">
+      <c r="B77" s="24" t="inlineStr">
         <is>
           <t>11. Document Uploads &amp; Proofs</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>GitHub Profile Repository URL</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>githubUrl</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="C77" s="25" t="inlineStr">
+        <is>
+          <t>Government Aadhaar Card (Front &amp; Back)</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr">
+        <is>
+          <t>docAadhaar</t>
+        </is>
+      </c>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F77" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G77" s="24" t="inlineStr">
+        <is>
+          <t>Aadhaar Act 2016 / Sovereign Identity</t>
+        </is>
+      </c>
+      <c r="H77" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust UIDAI e-KYC / OCR</t>
+        </is>
+      </c>
+      <c r="I77" s="24" t="inlineStr">
+        <is>
+          <t>PDF, PNG, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J77" s="24" t="inlineStr">
+        <is>
+          <t>Aadhaar_Card_Masked.pdf</t>
+        </is>
+      </c>
+      <c r="K77" s="24" t="inlineStr">
+        <is>
+          <t>Primary sovereign identity &amp; age proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="21" customHeight="1">
+      <c r="A78" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C78" s="28" t="inlineStr">
+        <is>
+          <t>Income Tax PAN Card Copy</t>
+        </is>
+      </c>
+      <c r="D78" s="27" t="inlineStr">
+        <is>
+          <t>docPan</t>
+        </is>
+      </c>
+      <c r="E78" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F78" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G78" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Act 1961 / Form 16</t>
+        </is>
+      </c>
+      <c r="H78" s="27" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust NSDL PAN Verification</t>
+        </is>
+      </c>
+      <c r="I78" s="27" t="inlineStr">
+        <is>
+          <t>PDF, PNG, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J78" s="27" t="inlineStr">
+        <is>
+          <t>PAN_Card_Color_Scan.jpg</t>
+        </is>
+      </c>
+      <c r="K78" s="27" t="inlineStr">
+        <is>
+          <t>Statutory tax deduction &amp; TAN linkage</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="21" customHeight="1">
+      <c r="A79" s="23" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C79" s="25" t="inlineStr">
+        <is>
+          <t>Formal Passport Size Photograph</t>
+        </is>
+      </c>
+      <c r="D79" s="24" t="inlineStr">
+        <is>
+          <t>docPassportPhoto</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>File Upload / Live Photo Capture</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G79" s="24" t="inlineStr">
+        <is>
+          <t>Corporate ID Badge / Labor Welfare Form</t>
+        </is>
+      </c>
+      <c r="H79" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust AI Face Biometrics</t>
+        </is>
+      </c>
+      <c r="I79" s="24" t="inlineStr">
+        <is>
+          <t>JPG, PNG (White Background, Max 5MB)</t>
+        </is>
+      </c>
+      <c r="J79" s="24" t="inlineStr">
+        <is>
+          <t>Employee_Formal_Photo.jpg</t>
+        </is>
+      </c>
+      <c r="K79" s="24" t="inlineStr">
+        <is>
+          <t>Employee ID card &amp; face biometric record</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="21" customHeight="1">
+      <c r="A80" s="26" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C80" s="28" t="inlineStr">
+        <is>
+          <t>Official Specimen Signature on Paper</t>
+        </is>
+      </c>
+      <c r="D80" s="27" t="inlineStr">
+        <is>
+          <t>docSpecimenSignature</t>
+        </is>
+      </c>
+      <c r="E80" s="27" t="inlineStr">
+        <is>
+          <t>File Upload / Digital Canvas</t>
+        </is>
+      </c>
+      <c r="F80" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G80" s="27" t="inlineStr">
+        <is>
+          <t>Indian Contract Act 1872 / Form F Gratuity</t>
+        </is>
+      </c>
+      <c r="H80" s="27" t="inlineStr">
+        <is>
+          <t>Internal Audit Vault Signature</t>
+        </is>
+      </c>
+      <c r="I80" s="27" t="inlineStr">
+        <is>
+          <t>PNG, JPG (Clear Signature, Max 2MB)</t>
+        </is>
+      </c>
+      <c r="J80" s="27" t="inlineStr">
+        <is>
+          <t>Specimen_Signature_Sample.png</t>
+        </is>
+      </c>
+      <c r="K80" s="27" t="inlineStr">
+        <is>
+          <t>Statutory nomination &amp; bank payroll execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="23" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C81" s="25" t="inlineStr">
+        <is>
+          <t>Passport / Driving License / Voter ID</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="inlineStr">
+        <is>
+          <t>docPassportOrDl</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G81" s="24" t="inlineStr">
+        <is>
+          <t>Secondary Sovereign ID / MoRTH / MEA</t>
+        </is>
+      </c>
+      <c r="H81" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust MoRTH / MEA Gateway</t>
+        </is>
+      </c>
+      <c r="I81" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J81" s="24" t="inlineStr">
+        <is>
+          <t>Passport_First_Last_Page.pdf</t>
+        </is>
+      </c>
+      <c r="K81" s="24" t="inlineStr">
+        <is>
+          <t>Secondary identity &amp; international travel readiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="26" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C82" s="28" t="inlineStr">
+        <is>
+          <t>Highest Degree / Convocation Certificate</t>
+        </is>
+      </c>
+      <c r="D82" s="27" t="inlineStr">
+        <is>
+          <t>docDegreeCert</t>
+        </is>
+      </c>
+      <c r="E82" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F82" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G82" s="27" t="inlineStr">
+        <is>
+          <t>Academic Qualifications &amp; Skill Audit</t>
+        </is>
+      </c>
+      <c r="H82" s="27" t="inlineStr">
+        <is>
+          <t>National Academic Depository (NAD) / University</t>
+        </is>
+      </c>
+      <c r="I82" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J82" s="27" t="inlineStr">
+        <is>
+          <t>BTech_Degree_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K82" s="27" t="inlineStr">
+        <is>
+          <t>Highest qualification credential authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="23" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C83" s="25" t="inlineStr">
+        <is>
+          <t>Consolidated / All Semester Marksheets</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr">
+        <is>
+          <t>docConsolidatedMarksheet</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F83" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="inlineStr">
+        <is>
+          <t>Academic Score &amp; Integrity Check</t>
+        </is>
+      </c>
+      <c r="H83" s="24" t="inlineStr">
+        <is>
+          <t>NAD / State Technical Board</t>
+        </is>
+      </c>
+      <c r="I83" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 15MB)</t>
+        </is>
+      </c>
+      <c r="J83" s="24" t="inlineStr">
+        <is>
+          <t>Consolidated_Marksheet_AllSem.pdf</t>
+        </is>
+      </c>
+      <c r="K83" s="24" t="inlineStr">
+        <is>
+          <t>Cumulative academic performance verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C84" s="28" t="inlineStr">
+        <is>
+          <t>Higher Secondary (12th / 10+2) Marksheet</t>
+        </is>
+      </c>
+      <c r="D84" s="27" t="inlineStr">
+        <is>
+          <t>docHsc12thMarksheet</t>
+        </is>
+      </c>
+      <c r="E84" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F84" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G84" s="27" t="inlineStr">
+        <is>
+          <t>School Education Board Verification</t>
+        </is>
+      </c>
+      <c r="H84" s="27" t="inlineStr">
+        <is>
+          <t>State / CBSE Education Board</t>
+        </is>
+      </c>
+      <c r="I84" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J84" s="27" t="inlineStr">
+        <is>
+          <t>HSC_12th_Marksheet.pdf</t>
+        </is>
+      </c>
+      <c r="K84" s="27" t="inlineStr">
+        <is>
+          <t>Intermediate secondary education record</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="23" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C85" s="25" t="inlineStr">
+        <is>
+          <t>SSLC (10th Standard) Marksheet / DOB Proof</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>docSslc10thMarksheet</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>Proof of Age / Factories Act Section 67</t>
+        </is>
+      </c>
+      <c r="H85" s="24" t="inlineStr">
+        <is>
+          <t>State Secondary Board</t>
+        </is>
+      </c>
+      <c r="I85" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J85" s="24" t="inlineStr">
+        <is>
+          <t>SSLC_10th_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K85" s="24" t="inlineStr">
+        <is>
+          <t>Statutory age &amp; date of birth authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C86" s="28" t="inlineStr">
+        <is>
+          <t>Previous Employer Official Relieving Letter</t>
+        </is>
+      </c>
+      <c r="D86" s="27" t="inlineStr">
+        <is>
+          <t>docRelievingLetter</t>
+        </is>
+      </c>
+      <c r="E86" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F86" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G86" s="27" t="inlineStr">
+        <is>
+          <t>Employment Separation &amp; Formal Exit</t>
+        </is>
+      </c>
+      <c r="H86" s="27" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust EPFO Service Passbook</t>
+        </is>
+      </c>
+      <c r="I86" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J86" s="27" t="inlineStr">
+        <is>
+          <t>Infosys_Relieving_Letter.pdf</t>
+        </is>
+      </c>
+      <c r="K86" s="27" t="inlineStr">
+        <is>
+          <t>Honorable exit and separation verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="23" t="n">
+        <v>83</v>
+      </c>
+      <c r="B87" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C87" s="25" t="inlineStr">
+        <is>
+          <t>Previous Service / Experience Certificate</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="inlineStr">
+        <is>
+          <t>docExperienceCertificate</t>
+        </is>
+      </c>
+      <c r="E87" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G87" s="24" t="inlineStr">
+        <is>
+          <t>Service Experience &amp; Band Hierarchy</t>
+        </is>
+      </c>
+      <c r="H87" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust EPFO &amp; HR Verification</t>
+        </is>
+      </c>
+      <c r="I87" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J87" s="24" t="inlineStr">
+        <is>
+          <t>Service_Experience_Letter.pdf</t>
+        </is>
+      </c>
+      <c r="K87" s="24" t="inlineStr">
+        <is>
+          <t>Past tenure &amp; role comparability audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="B88" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C88" s="28" t="inlineStr">
+        <is>
+          <t>Last 3 Months Consecutive Salary Slips</t>
+        </is>
+      </c>
+      <c r="D88" s="27" t="inlineStr">
+        <is>
+          <t>docSalarySlips3Months</t>
+        </is>
+      </c>
+      <c r="E88" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F88" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G88" s="27" t="inlineStr">
+        <is>
+          <t>Compensation &amp; Income Tax Form 16</t>
+        </is>
+      </c>
+      <c r="H88" s="27" t="inlineStr">
+        <is>
+          <t>Bank Payroll Deposit Matching</t>
+        </is>
+      </c>
+      <c r="I88" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 15MB)</t>
+        </is>
+      </c>
+      <c r="J88" s="27" t="inlineStr">
+        <is>
+          <t>Payslips_Last_3_Months.pdf</t>
+        </is>
+      </c>
+      <c r="K88" s="27" t="inlineStr">
+        <is>
+          <t>Last drawn CTC benchmarking &amp; tax continuity</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="23" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C89" s="25" t="inlineStr">
+        <is>
+          <t>Bank Pre-Printed Cancelled Cheque / Passbook</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="inlineStr">
+        <is>
+          <t>docBankCancelledCheque</t>
+        </is>
+      </c>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G89" s="24" t="inlineStr">
+        <is>
+          <t>Payment of Wages Act 1936 / Direct Credit</t>
+        </is>
+      </c>
+      <c r="H89" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust NPCI IMPS Penny Drop</t>
+        </is>
+      </c>
+      <c r="I89" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG, PNG (Showing Name &amp; IFSC)</t>
+        </is>
+      </c>
+      <c r="J89" s="24" t="inlineStr">
+        <is>
+          <t>HDFC_Cancelled_Cheque.jpg</t>
+        </is>
+      </c>
+      <c r="K89" s="24" t="inlineStr">
+        <is>
+          <t>Penny drop verified salary account proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C90" s="28" t="inlineStr">
+        <is>
+          <t>Previous Employer Form 16 / Tax Statement</t>
+        </is>
+      </c>
+      <c r="D90" s="27" t="inlineStr">
+        <is>
+          <t>docForm16TaxStatement</t>
+        </is>
+      </c>
+      <c r="E90" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F90" s="26" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="G90" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Act 1961 Section 203</t>
+        </is>
+      </c>
+      <c r="H90" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Traces Portal</t>
+        </is>
+      </c>
+      <c r="I90" s="27" t="inlineStr">
+        <is>
+          <t>PDF (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J90" s="27" t="inlineStr">
+        <is>
+          <t>Form16_PartA_PartB.pdf</t>
+        </is>
+      </c>
+      <c r="K90" s="27" t="inlineStr">
+        <is>
+          <t>TDS calculation &amp; mid-year tax continuity</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="23" t="n">
+        <v>87</v>
+      </c>
+      <c r="B91" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C91" s="25" t="inlineStr">
+        <is>
+          <t>Pre-Employment Medical Fitness Certificate</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="inlineStr">
+        <is>
+          <t>docMedicalFitnessCert</t>
+        </is>
+      </c>
+      <c r="E91" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G91" s="24" t="inlineStr">
+        <is>
+          <t>Occupational Health &amp; Group Insurance</t>
+        </is>
+      </c>
+      <c r="H91" s="24" t="inlineStr">
+        <is>
+          <t>Hospital / Registered Medical Practitioner</t>
+        </is>
+      </c>
+      <c r="I91" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J91" s="24" t="inlineStr">
+        <is>
+          <t>Medical_Fitness_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K91" s="24" t="inlineStr">
+        <is>
+          <t>Workplace physical fitness &amp; health insurance underwriting</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C92" s="28" t="inlineStr">
+        <is>
+          <t>Executed Non-Disclosure Agreement (NDA)</t>
+        </is>
+      </c>
+      <c r="D92" s="27" t="inlineStr">
+        <is>
+          <t>docSignedNda</t>
+        </is>
+      </c>
+      <c r="E92" s="27" t="inlineStr">
+        <is>
+          <t>File Upload / Checkbox Agreement</t>
+        </is>
+      </c>
+      <c r="F92" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G92" s="27" t="inlineStr">
+        <is>
+          <t>Indian Contract Act / Trade Secrets Protection</t>
+        </is>
+      </c>
+      <c r="H92" s="27" t="inlineStr">
+        <is>
+          <t>Internal Legal Compliance Hash</t>
+        </is>
+      </c>
+      <c r="I92" s="27" t="inlineStr">
+        <is>
+          <t>PDF / Digital Timestamp</t>
+        </is>
+      </c>
+      <c r="J92" s="27" t="inlineStr">
+        <is>
+          <t>Signed_NDA_IP_Assignment.pdf</t>
+        </is>
+      </c>
+      <c r="K92" s="27" t="inlineStr">
+        <is>
+          <t>Corporate confidentiality &amp; IP assignment execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="23" t="n">
+        <v>89</v>
+      </c>
+      <c r="B93" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C93" s="25" t="inlineStr">
+        <is>
+          <t>GitHub Profile / Code Repository URL</t>
+        </is>
+      </c>
+      <c r="D93" s="24" t="inlineStr">
+        <is>
+          <t>docGithubUrl</t>
+        </is>
+      </c>
+      <c r="E93" s="24" t="inlineStr">
         <is>
           <t>URL Input</t>
         </is>
       </c>
-      <c r="F77" s="11" t="inlineStr">
+      <c r="F93" s="23" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="G77" s="10" t="inlineStr">
-        <is>
-          <t>Technical Skill Benchmark</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>CoinCircleTrust GitHub API</t>
-        </is>
-      </c>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>Valid URL `https://github.com/...`</t>
-        </is>
-      </c>
-      <c r="J77" s="10" t="inlineStr">
-        <is>
-          <t>https://github.com/developer-profile</t>
-        </is>
-      </c>
-      <c r="K77" s="10" t="inlineStr">
-        <is>
-          <t>Code contribution audit</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="21" customHeight="1">
-      <c r="A78" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="B78" s="22" t="inlineStr">
+      <c r="G93" s="24" t="inlineStr">
+        <is>
+          <t>Technical Skill Benchmarking</t>
+        </is>
+      </c>
+      <c r="H93" s="24" t="inlineStr">
+        <is>
+          <t>GitHub Public API</t>
+        </is>
+      </c>
+      <c r="I93" s="24" t="inlineStr">
+        <is>
+          <t>Valid HTTPS URL</t>
+        </is>
+      </c>
+      <c r="J93" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/muthukumar-dev</t>
+        </is>
+      </c>
+      <c r="K93" s="24" t="inlineStr">
+        <is>
+          <t>Open-source code quality &amp; architecture portfolio</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="26" t="n">
+        <v>90</v>
+      </c>
+      <c r="B94" s="27" t="inlineStr">
         <is>
           <t>11. Document Uploads &amp; Proofs</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>LinkedIn Profile URL</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>linkedInUrl</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="C94" s="28" t="inlineStr">
+        <is>
+          <t>Technical Portfolio / Project Showcase URL</t>
+        </is>
+      </c>
+      <c r="D94" s="27" t="inlineStr">
+        <is>
+          <t>docPortfolioUrl</t>
+        </is>
+      </c>
+      <c r="E94" s="27" t="inlineStr">
         <is>
           <t>URL Input</t>
         </is>
       </c>
-      <c r="F78" s="11" t="inlineStr">
+      <c r="F94" s="26" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="G78" s="10" t="inlineStr">
-        <is>
-          <t>Professional Social Presence</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>Valid URL `https://linkedin.com/in/...`</t>
-        </is>
-      </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/muthukumar-dev</t>
-        </is>
-      </c>
-      <c r="J78" s="10" t="inlineStr">
-        <is>
-          <t>Professional portfolio</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="21" customHeight="1">
-      <c r="A79" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="B79" s="22" t="inlineStr">
+      <c r="G94" s="27" t="inlineStr">
+        <is>
+          <t>Professional Web Presence</t>
+        </is>
+      </c>
+      <c r="H94" s="27" t="inlineStr">
+        <is>
+          <t>Live Portfolio Domain</t>
+        </is>
+      </c>
+      <c r="I94" s="27" t="inlineStr">
+        <is>
+          <t>Valid HTTPS URL</t>
+        </is>
+      </c>
+      <c r="J94" s="27" t="inlineStr">
+        <is>
+          <t>https://muthu-portfolio.dev</t>
+        </is>
+      </c>
+      <c r="K94" s="27" t="inlineStr">
+        <is>
+          <t>Full-stack project demonstrations and live apps</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="23" t="n">
+        <v>91</v>
+      </c>
+      <c r="B95" s="24" t="inlineStr">
         <is>
           <t>11. Document Uploads &amp; Proofs</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>Moonlighting Non-Engagement Declaration</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>moonlightingDeclaration</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>Checkbox Agreement</t>
-        </is>
-      </c>
-      <c r="F79" s="9" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="G79" s="10" t="inlineStr">
-        <is>
-          <t>IT Industry Dual Employment Code</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>CoinCircleTrust EPFO Overlap Engine</t>
-        </is>
-      </c>
-      <c r="I79" s="10" t="inlineStr">
-        <is>
-          <t>Boolean (True / False)</t>
-        </is>
-      </c>
-      <c r="J79" s="10" t="inlineStr">
-        <is>
-          <t>True (Agreed &amp; Signed)</t>
-        </is>
-      </c>
-      <c r="K79" s="10" t="inlineStr">
-        <is>
-          <t>Prevention of unauthorized concurrent employment</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="21" customHeight="1">
-      <c r="A80" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="B80" s="22" t="inlineStr">
-        <is>
-          <t>11. Document Uploads &amp; Proofs</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>Non-Disclosure &amp; IP Assignment (NDA)</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>ndaIpAssignment</t>
-        </is>
-      </c>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>Checkbox Agreement</t>
-        </is>
-      </c>
-      <c r="F80" s="9" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="G80" s="10" t="inlineStr">
-        <is>
-          <t>Corporate Confidentiality &amp; Patent Act</t>
-        </is>
-      </c>
-      <c r="H80" s="10" t="inlineStr">
-        <is>
-          <t>Digital Cryptographic Signature</t>
-        </is>
-      </c>
-      <c r="I80" s="10" t="inlineStr">
-        <is>
-          <t>Boolean (True / False)</t>
-        </is>
-      </c>
-      <c r="J80" s="10" t="inlineStr">
-        <is>
-          <t>True (Digitally Executed)</t>
-        </is>
-      </c>
-      <c r="K80" s="10" t="inlineStr">
-        <is>
-          <t>Protection of intellectual property &amp; trade secrets</t>
+      <c r="C95" s="25" t="inlineStr">
+        <is>
+          <t>Non-Moonlighting &amp; Exclusive Service Declaration</t>
+        </is>
+      </c>
+      <c r="D95" s="24" t="inlineStr">
+        <is>
+          <t>docMoonlightingDeclaration</t>
+        </is>
+      </c>
+      <c r="E95" s="24" t="inlineStr">
+        <is>
+          <t>Checkbox Agreement / Digital Sign</t>
+        </is>
+      </c>
+      <c r="F95" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G95" s="24" t="inlineStr">
+        <is>
+          <t>IT Industry Anti-Moonlighting Code</t>
+        </is>
+      </c>
+      <c r="H95" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust Dual Employment Audit</t>
+        </is>
+      </c>
+      <c r="I95" s="24" t="inlineStr">
+        <is>
+          <t>Digital Agreement Checkbox</t>
+        </is>
+      </c>
+      <c r="J95" s="24" t="inlineStr">
+        <is>
+          <t>True (Agreed &amp; Executed)</t>
+        </is>
+      </c>
+      <c r="K95" s="24" t="inlineStr">
+        <is>
+          <t>Zero moonlighting &amp; exclusive corporate commitment</t>
         </is>
       </c>
     </row>
@@ -4790,8 +5664,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K96"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -8724,167 +9598,1102 @@
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="22" t="inlineStr">
+      <c r="B77" s="24" t="inlineStr">
         <is>
           <t>11. Document Uploads &amp; Proofs</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C77" s="25" t="inlineStr">
+        <is>
+          <t>Government Aadhaar Card (Front &amp; Back)</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr">
+        <is>
+          <t>docAadhaar</t>
+        </is>
+      </c>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F77" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G77" s="24" t="inlineStr">
+        <is>
+          <t>Aadhaar Act 2016 / Sovereign Identity</t>
+        </is>
+      </c>
+      <c r="H77" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust UIDAI e-KYC / OCR</t>
+        </is>
+      </c>
+      <c r="I77" s="24" t="inlineStr">
+        <is>
+          <t>PDF, PNG, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J77" s="24" t="inlineStr">
+        <is>
+          <t>Aadhaar_Card_Masked.pdf</t>
+        </is>
+      </c>
+      <c r="K77" s="24" t="inlineStr">
+        <is>
+          <t>Primary sovereign identity &amp; age proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="21" customHeight="1">
+      <c r="A78" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C78" s="28" t="inlineStr">
+        <is>
+          <t>Income Tax PAN Card Copy</t>
+        </is>
+      </c>
+      <c r="D78" s="27" t="inlineStr">
+        <is>
+          <t>docPan</t>
+        </is>
+      </c>
+      <c r="E78" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F78" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G78" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Act 1961 / Form 16</t>
+        </is>
+      </c>
+      <c r="H78" s="27" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust NSDL PAN Verification</t>
+        </is>
+      </c>
+      <c r="I78" s="27" t="inlineStr">
+        <is>
+          <t>PDF, PNG, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J78" s="27" t="inlineStr">
+        <is>
+          <t>PAN_Card_Color_Scan.jpg</t>
+        </is>
+      </c>
+      <c r="K78" s="27" t="inlineStr">
+        <is>
+          <t>Statutory tax deduction &amp; TAN linkage</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="21" customHeight="1">
+      <c r="A79" s="23" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C79" s="25" t="inlineStr">
+        <is>
+          <t>Formal Passport Size Photograph</t>
+        </is>
+      </c>
+      <c r="D79" s="24" t="inlineStr">
+        <is>
+          <t>docPassportPhoto</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>File Upload / Live Photo Capture</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G79" s="24" t="inlineStr">
+        <is>
+          <t>Corporate ID Badge / Labor Welfare Form</t>
+        </is>
+      </c>
+      <c r="H79" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust AI Face Biometrics</t>
+        </is>
+      </c>
+      <c r="I79" s="24" t="inlineStr">
+        <is>
+          <t>JPG, PNG (White Background, Max 5MB)</t>
+        </is>
+      </c>
+      <c r="J79" s="24" t="inlineStr">
+        <is>
+          <t>Employee_Formal_Photo.jpg</t>
+        </is>
+      </c>
+      <c r="K79" s="24" t="inlineStr">
+        <is>
+          <t>Employee ID card &amp; face biometric record</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="26" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C80" s="28" t="inlineStr">
+        <is>
+          <t>Official Specimen Signature on Paper</t>
+        </is>
+      </c>
+      <c r="D80" s="27" t="inlineStr">
+        <is>
+          <t>docSpecimenSignature</t>
+        </is>
+      </c>
+      <c r="E80" s="27" t="inlineStr">
+        <is>
+          <t>File Upload / Digital Canvas</t>
+        </is>
+      </c>
+      <c r="F80" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G80" s="27" t="inlineStr">
+        <is>
+          <t>Indian Contract Act 1872 / Form F Gratuity</t>
+        </is>
+      </c>
+      <c r="H80" s="27" t="inlineStr">
+        <is>
+          <t>Internal Audit Vault Signature</t>
+        </is>
+      </c>
+      <c r="I80" s="27" t="inlineStr">
+        <is>
+          <t>PNG, JPG (Clear Signature, Max 2MB)</t>
+        </is>
+      </c>
+      <c r="J80" s="27" t="inlineStr">
+        <is>
+          <t>Specimen_Signature_Sample.png</t>
+        </is>
+      </c>
+      <c r="K80" s="27" t="inlineStr">
+        <is>
+          <t>Statutory nomination &amp; bank payroll execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="23" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C81" s="25" t="inlineStr">
+        <is>
+          <t>Passport / Driving License / Voter ID</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="inlineStr">
+        <is>
+          <t>docPassportOrDl</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G81" s="24" t="inlineStr">
+        <is>
+          <t>Secondary Sovereign ID / MoRTH / MEA</t>
+        </is>
+      </c>
+      <c r="H81" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust MoRTH / MEA Gateway</t>
+        </is>
+      </c>
+      <c r="I81" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J81" s="24" t="inlineStr">
+        <is>
+          <t>Passport_First_Last_Page.pdf</t>
+        </is>
+      </c>
+      <c r="K81" s="24" t="inlineStr">
+        <is>
+          <t>Secondary identity &amp; international travel readiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="26" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C82" s="28" t="inlineStr">
+        <is>
+          <t>Highest Degree / Convocation Certificate</t>
+        </is>
+      </c>
+      <c r="D82" s="27" t="inlineStr">
+        <is>
+          <t>docDegreeCert</t>
+        </is>
+      </c>
+      <c r="E82" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F82" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G82" s="27" t="inlineStr">
+        <is>
+          <t>Academic Qualifications &amp; Skill Audit</t>
+        </is>
+      </c>
+      <c r="H82" s="27" t="inlineStr">
+        <is>
+          <t>National Academic Depository (NAD) / University</t>
+        </is>
+      </c>
+      <c r="I82" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J82" s="27" t="inlineStr">
+        <is>
+          <t>BTech_Degree_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K82" s="27" t="inlineStr">
+        <is>
+          <t>Highest qualification credential authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="23" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C83" s="25" t="inlineStr">
+        <is>
+          <t>Consolidated / All Semester Marksheets</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr">
+        <is>
+          <t>docConsolidatedMarksheet</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F83" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="inlineStr">
+        <is>
+          <t>Academic Score &amp; Integrity Check</t>
+        </is>
+      </c>
+      <c r="H83" s="24" t="inlineStr">
+        <is>
+          <t>NAD / State Technical Board</t>
+        </is>
+      </c>
+      <c r="I83" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 15MB)</t>
+        </is>
+      </c>
+      <c r="J83" s="24" t="inlineStr">
+        <is>
+          <t>Consolidated_Marksheet_AllSem.pdf</t>
+        </is>
+      </c>
+      <c r="K83" s="24" t="inlineStr">
+        <is>
+          <t>Cumulative academic performance verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C84" s="28" t="inlineStr">
+        <is>
+          <t>Higher Secondary (12th / 10+2) Marksheet</t>
+        </is>
+      </c>
+      <c r="D84" s="27" t="inlineStr">
+        <is>
+          <t>docHsc12thMarksheet</t>
+        </is>
+      </c>
+      <c r="E84" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F84" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G84" s="27" t="inlineStr">
+        <is>
+          <t>School Education Board Verification</t>
+        </is>
+      </c>
+      <c r="H84" s="27" t="inlineStr">
+        <is>
+          <t>State / CBSE Education Board</t>
+        </is>
+      </c>
+      <c r="I84" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J84" s="27" t="inlineStr">
+        <is>
+          <t>HSC_12th_Marksheet.pdf</t>
+        </is>
+      </c>
+      <c r="K84" s="27" t="inlineStr">
+        <is>
+          <t>Intermediate secondary education record</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="23" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C85" s="25" t="inlineStr">
+        <is>
+          <t>SSLC (10th Standard) Marksheet / DOB Proof</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>docSslc10thMarksheet</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>Proof of Age / Factories Act Section 67</t>
+        </is>
+      </c>
+      <c r="H85" s="24" t="inlineStr">
+        <is>
+          <t>State Secondary Board</t>
+        </is>
+      </c>
+      <c r="I85" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J85" s="24" t="inlineStr">
+        <is>
+          <t>SSLC_10th_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K85" s="24" t="inlineStr">
+        <is>
+          <t>Statutory age &amp; date of birth authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C86" s="28" t="inlineStr">
+        <is>
+          <t>Previous Employer Official Relieving Letter</t>
+        </is>
+      </c>
+      <c r="D86" s="27" t="inlineStr">
+        <is>
+          <t>docRelievingLetter</t>
+        </is>
+      </c>
+      <c r="E86" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F86" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G86" s="27" t="inlineStr">
+        <is>
+          <t>Employment Separation &amp; Formal Exit</t>
+        </is>
+      </c>
+      <c r="H86" s="27" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust EPFO Service Passbook</t>
+        </is>
+      </c>
+      <c r="I86" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J86" s="27" t="inlineStr">
+        <is>
+          <t>Infosys_Relieving_Letter.pdf</t>
+        </is>
+      </c>
+      <c r="K86" s="27" t="inlineStr">
+        <is>
+          <t>Honorable exit and separation verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="23" t="n">
+        <v>83</v>
+      </c>
+      <c r="B87" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C87" s="25" t="inlineStr">
+        <is>
+          <t>Previous Service / Experience Certificate</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="inlineStr">
+        <is>
+          <t>docExperienceCertificate</t>
+        </is>
+      </c>
+      <c r="E87" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G87" s="24" t="inlineStr">
+        <is>
+          <t>Service Experience &amp; Band Hierarchy</t>
+        </is>
+      </c>
+      <c r="H87" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust EPFO &amp; HR Verification</t>
+        </is>
+      </c>
+      <c r="I87" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J87" s="24" t="inlineStr">
+        <is>
+          <t>Service_Experience_Letter.pdf</t>
+        </is>
+      </c>
+      <c r="K87" s="24" t="inlineStr">
+        <is>
+          <t>Past tenure &amp; role comparability audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="B88" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C88" s="28" t="inlineStr">
+        <is>
+          <t>Last 3 Months Consecutive Salary Slips</t>
+        </is>
+      </c>
+      <c r="D88" s="27" t="inlineStr">
+        <is>
+          <t>docSalarySlips3Months</t>
+        </is>
+      </c>
+      <c r="E88" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F88" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G88" s="27" t="inlineStr">
+        <is>
+          <t>Compensation &amp; Income Tax Form 16</t>
+        </is>
+      </c>
+      <c r="H88" s="27" t="inlineStr">
+        <is>
+          <t>Bank Payroll Deposit Matching</t>
+        </is>
+      </c>
+      <c r="I88" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 15MB)</t>
+        </is>
+      </c>
+      <c r="J88" s="27" t="inlineStr">
+        <is>
+          <t>Payslips_Last_3_Months.pdf</t>
+        </is>
+      </c>
+      <c r="K88" s="27" t="inlineStr">
+        <is>
+          <t>Last drawn CTC benchmarking &amp; tax continuity</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="23" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C89" s="25" t="inlineStr">
+        <is>
+          <t>Bank Pre-Printed Cancelled Cheque / Passbook</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="inlineStr">
+        <is>
+          <t>docBankCancelledCheque</t>
+        </is>
+      </c>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G89" s="24" t="inlineStr">
+        <is>
+          <t>Payment of Wages Act 1936 / Direct Credit</t>
+        </is>
+      </c>
+      <c r="H89" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust NPCI IMPS Penny Drop</t>
+        </is>
+      </c>
+      <c r="I89" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG, PNG (Showing Name &amp; IFSC)</t>
+        </is>
+      </c>
+      <c r="J89" s="24" t="inlineStr">
+        <is>
+          <t>HDFC_Cancelled_Cheque.jpg</t>
+        </is>
+      </c>
+      <c r="K89" s="24" t="inlineStr">
+        <is>
+          <t>Penny drop verified salary account proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C90" s="28" t="inlineStr">
+        <is>
+          <t>Previous Employer Form 16 / Tax Statement</t>
+        </is>
+      </c>
+      <c r="D90" s="27" t="inlineStr">
+        <is>
+          <t>docForm16TaxStatement</t>
+        </is>
+      </c>
+      <c r="E90" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F90" s="26" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="G90" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Act 1961 Section 203</t>
+        </is>
+      </c>
+      <c r="H90" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Traces Portal</t>
+        </is>
+      </c>
+      <c r="I90" s="27" t="inlineStr">
+        <is>
+          <t>PDF (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J90" s="27" t="inlineStr">
+        <is>
+          <t>Form16_PartA_PartB.pdf</t>
+        </is>
+      </c>
+      <c r="K90" s="27" t="inlineStr">
+        <is>
+          <t>TDS calculation &amp; mid-year tax continuity</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="23" t="n">
+        <v>87</v>
+      </c>
+      <c r="B91" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C91" s="25" t="inlineStr">
+        <is>
+          <t>Pre-Employment Medical Fitness Certificate</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="inlineStr">
+        <is>
+          <t>docMedicalFitnessCert</t>
+        </is>
+      </c>
+      <c r="E91" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G91" s="24" t="inlineStr">
+        <is>
+          <t>Occupational Health &amp; Group Insurance</t>
+        </is>
+      </c>
+      <c r="H91" s="24" t="inlineStr">
+        <is>
+          <t>Hospital / Registered Medical Practitioner</t>
+        </is>
+      </c>
+      <c r="I91" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J91" s="24" t="inlineStr">
+        <is>
+          <t>Medical_Fitness_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K91" s="24" t="inlineStr">
+        <is>
+          <t>Workplace physical fitness &amp; health insurance underwriting</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C92" s="28" t="inlineStr">
+        <is>
+          <t>Executed Non-Disclosure Agreement (NDA)</t>
+        </is>
+      </c>
+      <c r="D92" s="27" t="inlineStr">
+        <is>
+          <t>docSignedNda</t>
+        </is>
+      </c>
+      <c r="E92" s="27" t="inlineStr">
+        <is>
+          <t>File Upload / Checkbox Agreement</t>
+        </is>
+      </c>
+      <c r="F92" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G92" s="27" t="inlineStr">
+        <is>
+          <t>Indian Contract Act / Trade Secrets Protection</t>
+        </is>
+      </c>
+      <c r="H92" s="27" t="inlineStr">
+        <is>
+          <t>Internal Legal Compliance Hash</t>
+        </is>
+      </c>
+      <c r="I92" s="27" t="inlineStr">
+        <is>
+          <t>PDF / Digital Timestamp</t>
+        </is>
+      </c>
+      <c r="J92" s="27" t="inlineStr">
+        <is>
+          <t>Signed_NDA_IP_Assignment.pdf</t>
+        </is>
+      </c>
+      <c r="K92" s="27" t="inlineStr">
+        <is>
+          <t>Corporate confidentiality &amp; IP assignment execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="23" t="n">
+        <v>89</v>
+      </c>
+      <c r="B93" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C93" s="25" t="inlineStr">
         <is>
           <t>ITI / Vocational Trade Certificate (NCVT)</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D93" s="24" t="inlineStr">
         <is>
           <t>docTradeCert</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>File Upload</t>
-        </is>
-      </c>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="G77" s="10" t="inlineStr">
-        <is>
-          <t>Factory Skills Record</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>Trade Registry Verification</t>
-        </is>
-      </c>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>PDF / JPG &lt; 5MB</t>
-        </is>
-      </c>
-      <c r="J77" s="10" t="inlineStr">
-        <is>
-          <t>ITI_Fitter_Certificate.pdf</t>
-        </is>
-      </c>
-      <c r="K77" s="10" t="inlineStr">
-        <is>
-          <t>Trade qualification proof</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="21" customHeight="1">
-      <c r="A78" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="B78" s="22" t="inlineStr">
+      <c r="E93" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F93" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G93" s="24" t="inlineStr">
+        <is>
+          <t>Apprentices Act 1961 / Factory Skills Record</t>
+        </is>
+      </c>
+      <c r="H93" s="24" t="inlineStr">
+        <is>
+          <t>NCVT MIS Portal</t>
+        </is>
+      </c>
+      <c r="I93" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J93" s="24" t="inlineStr">
+        <is>
+          <t>ITI_Fitter_Machinist_NCVT.pdf</t>
+        </is>
+      </c>
+      <c r="K93" s="24" t="inlineStr">
+        <is>
+          <t>Technical trade competency &amp; workshop certification</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="26" t="n">
+        <v>90</v>
+      </c>
+      <c r="B94" s="27" t="inlineStr">
         <is>
           <t>11. Document Uploads &amp; Proofs</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>Pre-Employment Medical Fitness Report (Form 33)</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="C94" s="28" t="inlineStr">
+        <is>
+          <t>Pre-Employment Medical Fitness (Form 33)</t>
+        </is>
+      </c>
+      <c r="D94" s="27" t="inlineStr">
         <is>
           <t>docForm33</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>File Upload</t>
-        </is>
-      </c>
-      <c r="F78" s="9" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="G78" s="10" t="inlineStr">
-        <is>
-          <t>Factory Act 1948 Section 41C</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>Authorized Factory Medical Officer</t>
-        </is>
-      </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>PDF File &lt; 5MB</t>
-        </is>
-      </c>
-      <c r="J78" s="10" t="inlineStr">
-        <is>
-          <t>Form33_Fitness_Report.pdf</t>
-        </is>
-      </c>
-      <c r="K78" s="10" t="inlineStr">
-        <is>
-          <t>Medical fitness for heavy plant machinery</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="21" customHeight="1">
-      <c r="A79" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="B79" s="22" t="inlineStr">
+      <c r="E94" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F94" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G94" s="27" t="inlineStr">
+        <is>
+          <t>Factories Act 1948 Section 41C / Form 33</t>
+        </is>
+      </c>
+      <c r="H94" s="27" t="inlineStr">
+        <is>
+          <t>Certified Factory Surgeon</t>
+        </is>
+      </c>
+      <c r="I94" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J94" s="27" t="inlineStr">
+        <is>
+          <t>Form33_Factory_Health_Report.pdf</t>
+        </is>
+      </c>
+      <c r="K94" s="27" t="inlineStr">
+        <is>
+          <t>Statutory factory floor hazardous process clearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="23" t="n">
+        <v>91</v>
+      </c>
+      <c r="B95" s="24" t="inlineStr">
         <is>
           <t>11. Document Uploads &amp; Proofs</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C95" s="25" t="inlineStr">
         <is>
           <t>Forklift / Heavy Machinery Operator License</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>heavyOperatorLicense</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>Text Input</t>
-        </is>
-      </c>
-      <c r="F79" s="14" t="inlineStr">
+      <c r="D95" s="24" t="inlineStr">
+        <is>
+          <t>docHeavyOperatorLicense</t>
+        </is>
+      </c>
+      <c r="E95" s="24" t="inlineStr">
+        <is>
+          <t>File Upload / Text Input</t>
+        </is>
+      </c>
+      <c r="F95" s="23" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="G79" s="10" t="inlineStr">
-        <is>
-          <t>MoRTH Form 7 / Factory Inspection</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>CoinCircleTrust MoRTH DL API</t>
-        </is>
-      </c>
-      <c r="I79" s="10" t="inlineStr">
-        <is>
-          <t>License Number</t>
-        </is>
-      </c>
-      <c r="J79" s="10" t="inlineStr">
-        <is>
-          <t>KA0120190004128</t>
-        </is>
-      </c>
-      <c r="K79" s="10" t="inlineStr">
-        <is>
-          <t>Plant heavy machinery authorization</t>
+      <c r="G95" s="24" t="inlineStr">
+        <is>
+          <t>MoRTH Form 7 / Factory Inspection Norms</t>
+        </is>
+      </c>
+      <c r="H95" s="24" t="inlineStr">
+        <is>
+          <t>MoRTH Sarathi Transport Registry</t>
+        </is>
+      </c>
+      <c r="I95" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG or License Number</t>
+        </is>
+      </c>
+      <c r="J95" s="24" t="inlineStr">
+        <is>
+          <t>Forklift_Operator_License.pdf</t>
+        </is>
+      </c>
+      <c r="K95" s="24" t="inlineStr">
+        <is>
+          <t>Material handling &amp; heavy machinery safety compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="26" t="n">
+        <v>92</v>
+      </c>
+      <c r="B96" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C96" s="28" t="inlineStr">
+        <is>
+          <t>Factory Safety &amp; PPE Protocol Undertaking</t>
+        </is>
+      </c>
+      <c r="D96" s="27" t="inlineStr">
+        <is>
+          <t>docSafetyProtocolUndertaking</t>
+        </is>
+      </c>
+      <c r="E96" s="27" t="inlineStr">
+        <is>
+          <t>Checkbox Agreement</t>
+        </is>
+      </c>
+      <c r="F96" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G96" s="27" t="inlineStr">
+        <is>
+          <t>Occupational Safety, Health &amp; Working Conditions Code</t>
+        </is>
+      </c>
+      <c r="H96" s="27" t="inlineStr">
+        <is>
+          <t>Factory Safety Officer Hash</t>
+        </is>
+      </c>
+      <c r="I96" s="27" t="inlineStr">
+        <is>
+          <t>Digital Agreement Checkbox</t>
+        </is>
+      </c>
+      <c r="J96" s="27" t="inlineStr">
+        <is>
+          <t>True (Agreed &amp; Executed)</t>
+        </is>
+      </c>
+      <c r="K96" s="27" t="inlineStr">
+        <is>
+          <t>Zero-accident factory safety &amp; PPE compliance</t>
         </is>
       </c>
     </row>
@@ -8903,8 +10712,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K96"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -12837,167 +14646,1102 @@
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="22" t="inlineStr">
+      <c r="B77" s="24" t="inlineStr">
         <is>
           <t>11. Document Uploads &amp; Proofs</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>Chartered Accountant (CA) / CFA Membership Number</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>membershipNumber</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="C77" s="25" t="inlineStr">
+        <is>
+          <t>Government Aadhaar Card (Front &amp; Back)</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr">
+        <is>
+          <t>docAadhaar</t>
+        </is>
+      </c>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F77" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G77" s="24" t="inlineStr">
+        <is>
+          <t>Aadhaar Act 2016 / Sovereign Identity</t>
+        </is>
+      </c>
+      <c r="H77" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust UIDAI e-KYC / OCR</t>
+        </is>
+      </c>
+      <c r="I77" s="24" t="inlineStr">
+        <is>
+          <t>PDF, PNG, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J77" s="24" t="inlineStr">
+        <is>
+          <t>Aadhaar_Card_Masked.pdf</t>
+        </is>
+      </c>
+      <c r="K77" s="24" t="inlineStr">
+        <is>
+          <t>Primary sovereign identity &amp; age proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="21" customHeight="1">
+      <c r="A78" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C78" s="28" t="inlineStr">
+        <is>
+          <t>Income Tax PAN Card Copy</t>
+        </is>
+      </c>
+      <c r="D78" s="27" t="inlineStr">
+        <is>
+          <t>docPan</t>
+        </is>
+      </c>
+      <c r="E78" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F78" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G78" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Act 1961 / Form 16</t>
+        </is>
+      </c>
+      <c r="H78" s="27" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust NSDL PAN Verification</t>
+        </is>
+      </c>
+      <c r="I78" s="27" t="inlineStr">
+        <is>
+          <t>PDF, PNG, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J78" s="27" t="inlineStr">
+        <is>
+          <t>PAN_Card_Color_Scan.jpg</t>
+        </is>
+      </c>
+      <c r="K78" s="27" t="inlineStr">
+        <is>
+          <t>Statutory tax deduction &amp; TAN linkage</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="21" customHeight="1">
+      <c r="A79" s="23" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C79" s="25" t="inlineStr">
+        <is>
+          <t>Formal Passport Size Photograph</t>
+        </is>
+      </c>
+      <c r="D79" s="24" t="inlineStr">
+        <is>
+          <t>docPassportPhoto</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>File Upload / Live Photo Capture</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G79" s="24" t="inlineStr">
+        <is>
+          <t>Corporate ID Badge / Labor Welfare Form</t>
+        </is>
+      </c>
+      <c r="H79" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust AI Face Biometrics</t>
+        </is>
+      </c>
+      <c r="I79" s="24" t="inlineStr">
+        <is>
+          <t>JPG, PNG (White Background, Max 5MB)</t>
+        </is>
+      </c>
+      <c r="J79" s="24" t="inlineStr">
+        <is>
+          <t>Employee_Formal_Photo.jpg</t>
+        </is>
+      </c>
+      <c r="K79" s="24" t="inlineStr">
+        <is>
+          <t>Employee ID card &amp; face biometric record</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="26" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C80" s="28" t="inlineStr">
+        <is>
+          <t>Official Specimen Signature on Paper</t>
+        </is>
+      </c>
+      <c r="D80" s="27" t="inlineStr">
+        <is>
+          <t>docSpecimenSignature</t>
+        </is>
+      </c>
+      <c r="E80" s="27" t="inlineStr">
+        <is>
+          <t>File Upload / Digital Canvas</t>
+        </is>
+      </c>
+      <c r="F80" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G80" s="27" t="inlineStr">
+        <is>
+          <t>Indian Contract Act 1872 / Form F Gratuity</t>
+        </is>
+      </c>
+      <c r="H80" s="27" t="inlineStr">
+        <is>
+          <t>Internal Audit Vault Signature</t>
+        </is>
+      </c>
+      <c r="I80" s="27" t="inlineStr">
+        <is>
+          <t>PNG, JPG (Clear Signature, Max 2MB)</t>
+        </is>
+      </c>
+      <c r="J80" s="27" t="inlineStr">
+        <is>
+          <t>Specimen_Signature_Sample.png</t>
+        </is>
+      </c>
+      <c r="K80" s="27" t="inlineStr">
+        <is>
+          <t>Statutory nomination &amp; bank payroll execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="23" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C81" s="25" t="inlineStr">
+        <is>
+          <t>Passport / Driving License / Voter ID</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="inlineStr">
+        <is>
+          <t>docPassportOrDl</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G81" s="24" t="inlineStr">
+        <is>
+          <t>Secondary Sovereign ID / MoRTH / MEA</t>
+        </is>
+      </c>
+      <c r="H81" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust MoRTH / MEA Gateway</t>
+        </is>
+      </c>
+      <c r="I81" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J81" s="24" t="inlineStr">
+        <is>
+          <t>Passport_First_Last_Page.pdf</t>
+        </is>
+      </c>
+      <c r="K81" s="24" t="inlineStr">
+        <is>
+          <t>Secondary identity &amp; international travel readiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="26" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C82" s="28" t="inlineStr">
+        <is>
+          <t>Highest Degree / Convocation Certificate</t>
+        </is>
+      </c>
+      <c r="D82" s="27" t="inlineStr">
+        <is>
+          <t>docDegreeCert</t>
+        </is>
+      </c>
+      <c r="E82" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F82" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G82" s="27" t="inlineStr">
+        <is>
+          <t>Academic Qualifications &amp; Skill Audit</t>
+        </is>
+      </c>
+      <c r="H82" s="27" t="inlineStr">
+        <is>
+          <t>National Academic Depository (NAD) / University</t>
+        </is>
+      </c>
+      <c r="I82" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J82" s="27" t="inlineStr">
+        <is>
+          <t>BTech_Degree_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K82" s="27" t="inlineStr">
+        <is>
+          <t>Highest qualification credential authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="23" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C83" s="25" t="inlineStr">
+        <is>
+          <t>Consolidated / All Semester Marksheets</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr">
+        <is>
+          <t>docConsolidatedMarksheet</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F83" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="inlineStr">
+        <is>
+          <t>Academic Score &amp; Integrity Check</t>
+        </is>
+      </c>
+      <c r="H83" s="24" t="inlineStr">
+        <is>
+          <t>NAD / State Technical Board</t>
+        </is>
+      </c>
+      <c r="I83" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 15MB)</t>
+        </is>
+      </c>
+      <c r="J83" s="24" t="inlineStr">
+        <is>
+          <t>Consolidated_Marksheet_AllSem.pdf</t>
+        </is>
+      </c>
+      <c r="K83" s="24" t="inlineStr">
+        <is>
+          <t>Cumulative academic performance verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C84" s="28" t="inlineStr">
+        <is>
+          <t>Higher Secondary (12th / 10+2) Marksheet</t>
+        </is>
+      </c>
+      <c r="D84" s="27" t="inlineStr">
+        <is>
+          <t>docHsc12thMarksheet</t>
+        </is>
+      </c>
+      <c r="E84" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F84" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G84" s="27" t="inlineStr">
+        <is>
+          <t>School Education Board Verification</t>
+        </is>
+      </c>
+      <c r="H84" s="27" t="inlineStr">
+        <is>
+          <t>State / CBSE Education Board</t>
+        </is>
+      </c>
+      <c r="I84" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J84" s="27" t="inlineStr">
+        <is>
+          <t>HSC_12th_Marksheet.pdf</t>
+        </is>
+      </c>
+      <c r="K84" s="27" t="inlineStr">
+        <is>
+          <t>Intermediate secondary education record</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="23" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C85" s="25" t="inlineStr">
+        <is>
+          <t>SSLC (10th Standard) Marksheet / DOB Proof</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>docSslc10thMarksheet</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>Proof of Age / Factories Act Section 67</t>
+        </is>
+      </c>
+      <c r="H85" s="24" t="inlineStr">
+        <is>
+          <t>State Secondary Board</t>
+        </is>
+      </c>
+      <c r="I85" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J85" s="24" t="inlineStr">
+        <is>
+          <t>SSLC_10th_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K85" s="24" t="inlineStr">
+        <is>
+          <t>Statutory age &amp; date of birth authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C86" s="28" t="inlineStr">
+        <is>
+          <t>Previous Employer Official Relieving Letter</t>
+        </is>
+      </c>
+      <c r="D86" s="27" t="inlineStr">
+        <is>
+          <t>docRelievingLetter</t>
+        </is>
+      </c>
+      <c r="E86" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F86" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G86" s="27" t="inlineStr">
+        <is>
+          <t>Employment Separation &amp; Formal Exit</t>
+        </is>
+      </c>
+      <c r="H86" s="27" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust EPFO Service Passbook</t>
+        </is>
+      </c>
+      <c r="I86" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J86" s="27" t="inlineStr">
+        <is>
+          <t>Infosys_Relieving_Letter.pdf</t>
+        </is>
+      </c>
+      <c r="K86" s="27" t="inlineStr">
+        <is>
+          <t>Honorable exit and separation verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="23" t="n">
+        <v>83</v>
+      </c>
+      <c r="B87" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C87" s="25" t="inlineStr">
+        <is>
+          <t>Previous Service / Experience Certificate</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="inlineStr">
+        <is>
+          <t>docExperienceCertificate</t>
+        </is>
+      </c>
+      <c r="E87" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G87" s="24" t="inlineStr">
+        <is>
+          <t>Service Experience &amp; Band Hierarchy</t>
+        </is>
+      </c>
+      <c r="H87" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust EPFO &amp; HR Verification</t>
+        </is>
+      </c>
+      <c r="I87" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J87" s="24" t="inlineStr">
+        <is>
+          <t>Service_Experience_Letter.pdf</t>
+        </is>
+      </c>
+      <c r="K87" s="24" t="inlineStr">
+        <is>
+          <t>Past tenure &amp; role comparability audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="B88" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C88" s="28" t="inlineStr">
+        <is>
+          <t>Last 3 Months Consecutive Salary Slips</t>
+        </is>
+      </c>
+      <c r="D88" s="27" t="inlineStr">
+        <is>
+          <t>docSalarySlips3Months</t>
+        </is>
+      </c>
+      <c r="E88" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F88" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G88" s="27" t="inlineStr">
+        <is>
+          <t>Compensation &amp; Income Tax Form 16</t>
+        </is>
+      </c>
+      <c r="H88" s="27" t="inlineStr">
+        <is>
+          <t>Bank Payroll Deposit Matching</t>
+        </is>
+      </c>
+      <c r="I88" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 15MB)</t>
+        </is>
+      </c>
+      <c r="J88" s="27" t="inlineStr">
+        <is>
+          <t>Payslips_Last_3_Months.pdf</t>
+        </is>
+      </c>
+      <c r="K88" s="27" t="inlineStr">
+        <is>
+          <t>Last drawn CTC benchmarking &amp; tax continuity</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="23" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C89" s="25" t="inlineStr">
+        <is>
+          <t>Bank Pre-Printed Cancelled Cheque / Passbook</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="inlineStr">
+        <is>
+          <t>docBankCancelledCheque</t>
+        </is>
+      </c>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G89" s="24" t="inlineStr">
+        <is>
+          <t>Payment of Wages Act 1936 / Direct Credit</t>
+        </is>
+      </c>
+      <c r="H89" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust NPCI IMPS Penny Drop</t>
+        </is>
+      </c>
+      <c r="I89" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG, PNG (Showing Name &amp; IFSC)</t>
+        </is>
+      </c>
+      <c r="J89" s="24" t="inlineStr">
+        <is>
+          <t>HDFC_Cancelled_Cheque.jpg</t>
+        </is>
+      </c>
+      <c r="K89" s="24" t="inlineStr">
+        <is>
+          <t>Penny drop verified salary account proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C90" s="28" t="inlineStr">
+        <is>
+          <t>Previous Employer Form 16 / Tax Statement</t>
+        </is>
+      </c>
+      <c r="D90" s="27" t="inlineStr">
+        <is>
+          <t>docForm16TaxStatement</t>
+        </is>
+      </c>
+      <c r="E90" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F90" s="26" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="G90" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Act 1961 Section 203</t>
+        </is>
+      </c>
+      <c r="H90" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Traces Portal</t>
+        </is>
+      </c>
+      <c r="I90" s="27" t="inlineStr">
+        <is>
+          <t>PDF (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J90" s="27" t="inlineStr">
+        <is>
+          <t>Form16_PartA_PartB.pdf</t>
+        </is>
+      </c>
+      <c r="K90" s="27" t="inlineStr">
+        <is>
+          <t>TDS calculation &amp; mid-year tax continuity</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="23" t="n">
+        <v>87</v>
+      </c>
+      <c r="B91" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C91" s="25" t="inlineStr">
+        <is>
+          <t>Pre-Employment Medical Fitness Certificate</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="inlineStr">
+        <is>
+          <t>docMedicalFitnessCert</t>
+        </is>
+      </c>
+      <c r="E91" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G91" s="24" t="inlineStr">
+        <is>
+          <t>Occupational Health &amp; Group Insurance</t>
+        </is>
+      </c>
+      <c r="H91" s="24" t="inlineStr">
+        <is>
+          <t>Hospital / Registered Medical Practitioner</t>
+        </is>
+      </c>
+      <c r="I91" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J91" s="24" t="inlineStr">
+        <is>
+          <t>Medical_Fitness_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K91" s="24" t="inlineStr">
+        <is>
+          <t>Workplace physical fitness &amp; health insurance underwriting</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C92" s="28" t="inlineStr">
+        <is>
+          <t>Executed Non-Disclosure Agreement (NDA)</t>
+        </is>
+      </c>
+      <c r="D92" s="27" t="inlineStr">
+        <is>
+          <t>docSignedNda</t>
+        </is>
+      </c>
+      <c r="E92" s="27" t="inlineStr">
+        <is>
+          <t>File Upload / Checkbox Agreement</t>
+        </is>
+      </c>
+      <c r="F92" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G92" s="27" t="inlineStr">
+        <is>
+          <t>Indian Contract Act / Trade Secrets Protection</t>
+        </is>
+      </c>
+      <c r="H92" s="27" t="inlineStr">
+        <is>
+          <t>Internal Legal Compliance Hash</t>
+        </is>
+      </c>
+      <c r="I92" s="27" t="inlineStr">
+        <is>
+          <t>PDF / Digital Timestamp</t>
+        </is>
+      </c>
+      <c r="J92" s="27" t="inlineStr">
+        <is>
+          <t>Signed_NDA_IP_Assignment.pdf</t>
+        </is>
+      </c>
+      <c r="K92" s="27" t="inlineStr">
+        <is>
+          <t>Corporate confidentiality &amp; IP assignment execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="23" t="n">
+        <v>89</v>
+      </c>
+      <c r="B93" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C93" s="25" t="inlineStr">
+        <is>
+          <t>CA / CFA / CMA Professional Membership Certificate</t>
+        </is>
+      </c>
+      <c r="D93" s="24" t="inlineStr">
+        <is>
+          <t>docCaCfaMembership</t>
+        </is>
+      </c>
+      <c r="E93" s="24" t="inlineStr">
+        <is>
+          <t>File Upload / Text Input</t>
+        </is>
+      </c>
+      <c r="F93" s="23" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="G93" s="24" t="inlineStr">
+        <is>
+          <t>ICAI / CFA Institute / ICMAI Statutory Registry</t>
+        </is>
+      </c>
+      <c r="H93" s="24" t="inlineStr">
+        <is>
+          <t>ICAI / Professional Council Registry</t>
+        </is>
+      </c>
+      <c r="I93" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG or Membership Number</t>
+        </is>
+      </c>
+      <c r="J93" s="24" t="inlineStr">
+        <is>
+          <t>ICAI_Membership_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K93" s="24" t="inlineStr">
+        <is>
+          <t>Statutory audit &amp; financial advisory license check</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="26" t="n">
+        <v>90</v>
+      </c>
+      <c r="B94" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C94" s="28" t="inlineStr">
+        <is>
+          <t>Director Identification Number (DIN) Verification</t>
+        </is>
+      </c>
+      <c r="D94" s="27" t="inlineStr">
+        <is>
+          <t>docDinCheck</t>
+        </is>
+      </c>
+      <c r="E94" s="27" t="inlineStr">
         <is>
           <t>Text Input</t>
         </is>
       </c>
-      <c r="F77" s="14" t="inlineStr">
-        <is>
-          <t>Conditional</t>
-        </is>
-      </c>
-      <c r="G77" s="10" t="inlineStr">
-        <is>
-          <t>Statutory Professional Registry</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>ICAI Member Verification Portal</t>
-        </is>
-      </c>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>Registration Code</t>
-        </is>
-      </c>
-      <c r="J77" s="10" t="inlineStr">
-        <is>
-          <t>ICAI-MRN-419820</t>
-        </is>
-      </c>
-      <c r="K77" s="10" t="inlineStr">
-        <is>
-          <t>Authentication of certified standing</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="21" customHeight="1">
-      <c r="A78" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="B78" s="22" t="inlineStr">
+      <c r="F94" s="26" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G94" s="27" t="inlineStr">
+        <is>
+          <t>Companies Act 2013 Section 152</t>
+        </is>
+      </c>
+      <c r="H94" s="27" t="inlineStr">
+        <is>
+          <t>MCA21 Directorship Registry</t>
+        </is>
+      </c>
+      <c r="I94" s="27" t="inlineStr">
+        <is>
+          <t>8-Digit DIN `^[0-9]{8}$`</t>
+        </is>
+      </c>
+      <c r="J94" s="27" t="inlineStr">
+        <is>
+          <t>09812451</t>
+        </is>
+      </c>
+      <c r="K94" s="27" t="inlineStr">
+        <is>
+          <t>Director disqualification &amp; anti-moonlighting audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="23" t="n">
+        <v>91</v>
+      </c>
+      <c r="B95" s="24" t="inlineStr">
         <is>
           <t>11. Document Uploads &amp; Proofs</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>Director Identification Number (DIN) Check</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>dinNumber</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>Text Input</t>
-        </is>
-      </c>
-      <c r="F78" s="11" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="G78" s="10" t="inlineStr">
-        <is>
-          <t>Companies Act 2013 Section 152</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>CoinCircleTrust DIN to MCA API</t>
-        </is>
-      </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>8-digit numeric</t>
-        </is>
-      </c>
-      <c r="J78" s="10" t="inlineStr">
-        <is>
-          <t>08912340</t>
-        </is>
-      </c>
-      <c r="K78" s="10" t="inlineStr">
-        <is>
-          <t>Detection of unauthorized corporate directorships</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="21" customHeight="1">
-      <c r="A79" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="B79" s="22" t="inlineStr">
+      <c r="C95" s="25" t="inlineStr">
+        <is>
+          <t>SEBI Insider Trading (PIT) &amp; PEP Declaration</t>
+        </is>
+      </c>
+      <c r="D95" s="24" t="inlineStr">
+        <is>
+          <t>docInsiderTradingPolicy</t>
+        </is>
+      </c>
+      <c r="E95" s="24" t="inlineStr">
+        <is>
+          <t>Checkbox Agreement</t>
+        </is>
+      </c>
+      <c r="F95" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G95" s="24" t="inlineStr">
+        <is>
+          <t>SEBI (Prohibition of Insider Trading) Regulations 2015</t>
+        </is>
+      </c>
+      <c r="H95" s="24" t="inlineStr">
+        <is>
+          <t>Compliance Officer Audit Trail</t>
+        </is>
+      </c>
+      <c r="I95" s="24" t="inlineStr">
+        <is>
+          <t>Digital Agreement Checkbox</t>
+        </is>
+      </c>
+      <c r="J95" s="24" t="inlineStr">
+        <is>
+          <t>True (Signed &amp; Declared)</t>
+        </is>
+      </c>
+      <c r="K95" s="24" t="inlineStr">
+        <is>
+          <t>Securities compliance &amp; politically exposed persons check</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="26" t="n">
+        <v>92</v>
+      </c>
+      <c r="B96" s="27" t="inlineStr">
         <is>
           <t>11. Document Uploads &amp; Proofs</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>SEBI Insider Trading Blackout &amp; PEP Declaration</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>insiderTradingDeclaration</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>Checkbox Agreement</t>
-        </is>
-      </c>
-      <c r="F79" s="9" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="G79" s="10" t="inlineStr">
-        <is>
-          <t>SEBI Prohibition of Insider Trading (PIT)</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>SEBI Compliance Registry</t>
-        </is>
-      </c>
-      <c r="I79" s="10" t="inlineStr">
-        <is>
-          <t>Boolean (True / False)</t>
-        </is>
-      </c>
-      <c r="J79" s="10" t="inlineStr">
-        <is>
-          <t>True (Disclosed &amp; Agreed)</t>
-        </is>
-      </c>
-      <c r="K79" s="10" t="inlineStr">
-        <is>
-          <t>Compliance with SEBI trade blackout rules</t>
+      <c r="C96" s="28" t="inlineStr">
+        <is>
+          <t>Employee Fidelity Indemnity Bond Copy</t>
+        </is>
+      </c>
+      <c r="D96" s="27" t="inlineStr">
+        <is>
+          <t>docFidelityIndemnityBond</t>
+        </is>
+      </c>
+      <c r="E96" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F96" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G96" s="27" t="inlineStr">
+        <is>
+          <t>Banking Cash Handling &amp; Asset Protection</t>
+        </is>
+      </c>
+      <c r="H96" s="27" t="inlineStr">
+        <is>
+          <t>Insurance Fidelity Registry</t>
+        </is>
+      </c>
+      <c r="I96" s="27" t="inlineStr">
+        <is>
+          <t>PDF (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J96" s="27" t="inlineStr">
+        <is>
+          <t>Fidelity_Indemnity_Bond.pdf</t>
+        </is>
+      </c>
+      <c r="K96" s="27" t="inlineStr">
+        <is>
+          <t>Financial loss indemnity &amp; asset protection guarantee</t>
         </is>
       </c>
     </row>
@@ -13016,8 +15760,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K96"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -16950,167 +19694,1102 @@
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="22" t="inlineStr">
+      <c r="B77" s="24" t="inlineStr">
         <is>
           <t>11. Document Uploads &amp; Proofs</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>Commercial Driving License (DL) Number</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>dlNumber</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>Text Input</t>
-        </is>
-      </c>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="G77" s="10" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Act 1988 / MoRTH</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
+      <c r="C77" s="25" t="inlineStr">
+        <is>
+          <t>Government Aadhaar Card (Front &amp; Back)</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr">
+        <is>
+          <t>docAadhaar</t>
+        </is>
+      </c>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F77" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G77" s="24" t="inlineStr">
+        <is>
+          <t>Aadhaar Act 2016 / Sovereign Identity</t>
+        </is>
+      </c>
+      <c r="H77" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust UIDAI e-KYC / OCR</t>
+        </is>
+      </c>
+      <c r="I77" s="24" t="inlineStr">
+        <is>
+          <t>PDF, PNG, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J77" s="24" t="inlineStr">
+        <is>
+          <t>Aadhaar_Card_Masked.pdf</t>
+        </is>
+      </c>
+      <c r="K77" s="24" t="inlineStr">
+        <is>
+          <t>Primary sovereign identity &amp; age proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="21" customHeight="1">
+      <c r="A78" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C78" s="28" t="inlineStr">
+        <is>
+          <t>Income Tax PAN Card Copy</t>
+        </is>
+      </c>
+      <c r="D78" s="27" t="inlineStr">
+        <is>
+          <t>docPan</t>
+        </is>
+      </c>
+      <c r="E78" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F78" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G78" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Act 1961 / Form 16</t>
+        </is>
+      </c>
+      <c r="H78" s="27" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust NSDL PAN Verification</t>
+        </is>
+      </c>
+      <c r="I78" s="27" t="inlineStr">
+        <is>
+          <t>PDF, PNG, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J78" s="27" t="inlineStr">
+        <is>
+          <t>PAN_Card_Color_Scan.jpg</t>
+        </is>
+      </c>
+      <c r="K78" s="27" t="inlineStr">
+        <is>
+          <t>Statutory tax deduction &amp; TAN linkage</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="21" customHeight="1">
+      <c r="A79" s="23" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C79" s="25" t="inlineStr">
+        <is>
+          <t>Formal Passport Size Photograph</t>
+        </is>
+      </c>
+      <c r="D79" s="24" t="inlineStr">
+        <is>
+          <t>docPassportPhoto</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>File Upload / Live Photo Capture</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G79" s="24" t="inlineStr">
+        <is>
+          <t>Corporate ID Badge / Labor Welfare Form</t>
+        </is>
+      </c>
+      <c r="H79" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust AI Face Biometrics</t>
+        </is>
+      </c>
+      <c r="I79" s="24" t="inlineStr">
+        <is>
+          <t>JPG, PNG (White Background, Max 5MB)</t>
+        </is>
+      </c>
+      <c r="J79" s="24" t="inlineStr">
+        <is>
+          <t>Employee_Formal_Photo.jpg</t>
+        </is>
+      </c>
+      <c r="K79" s="24" t="inlineStr">
+        <is>
+          <t>Employee ID card &amp; face biometric record</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="26" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C80" s="28" t="inlineStr">
+        <is>
+          <t>Official Specimen Signature on Paper</t>
+        </is>
+      </c>
+      <c r="D80" s="27" t="inlineStr">
+        <is>
+          <t>docSpecimenSignature</t>
+        </is>
+      </c>
+      <c r="E80" s="27" t="inlineStr">
+        <is>
+          <t>File Upload / Digital Canvas</t>
+        </is>
+      </c>
+      <c r="F80" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G80" s="27" t="inlineStr">
+        <is>
+          <t>Indian Contract Act 1872 / Form F Gratuity</t>
+        </is>
+      </c>
+      <c r="H80" s="27" t="inlineStr">
+        <is>
+          <t>Internal Audit Vault Signature</t>
+        </is>
+      </c>
+      <c r="I80" s="27" t="inlineStr">
+        <is>
+          <t>PNG, JPG (Clear Signature, Max 2MB)</t>
+        </is>
+      </c>
+      <c r="J80" s="27" t="inlineStr">
+        <is>
+          <t>Specimen_Signature_Sample.png</t>
+        </is>
+      </c>
+      <c r="K80" s="27" t="inlineStr">
+        <is>
+          <t>Statutory nomination &amp; bank payroll execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="23" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C81" s="25" t="inlineStr">
+        <is>
+          <t>Passport / Driving License / Voter ID</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="inlineStr">
+        <is>
+          <t>docPassportOrDl</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G81" s="24" t="inlineStr">
+        <is>
+          <t>Secondary Sovereign ID / MoRTH / MEA</t>
+        </is>
+      </c>
+      <c r="H81" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust MoRTH / MEA Gateway</t>
+        </is>
+      </c>
+      <c r="I81" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J81" s="24" t="inlineStr">
+        <is>
+          <t>Passport_First_Last_Page.pdf</t>
+        </is>
+      </c>
+      <c r="K81" s="24" t="inlineStr">
+        <is>
+          <t>Secondary identity &amp; international travel readiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="26" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C82" s="28" t="inlineStr">
+        <is>
+          <t>Highest Degree / Convocation Certificate</t>
+        </is>
+      </c>
+      <c r="D82" s="27" t="inlineStr">
+        <is>
+          <t>docDegreeCert</t>
+        </is>
+      </c>
+      <c r="E82" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F82" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G82" s="27" t="inlineStr">
+        <is>
+          <t>Academic Qualifications &amp; Skill Audit</t>
+        </is>
+      </c>
+      <c r="H82" s="27" t="inlineStr">
+        <is>
+          <t>National Academic Depository (NAD) / University</t>
+        </is>
+      </c>
+      <c r="I82" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J82" s="27" t="inlineStr">
+        <is>
+          <t>BTech_Degree_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K82" s="27" t="inlineStr">
+        <is>
+          <t>Highest qualification credential authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="23" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C83" s="25" t="inlineStr">
+        <is>
+          <t>Consolidated / All Semester Marksheets</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr">
+        <is>
+          <t>docConsolidatedMarksheet</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F83" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="inlineStr">
+        <is>
+          <t>Academic Score &amp; Integrity Check</t>
+        </is>
+      </c>
+      <c r="H83" s="24" t="inlineStr">
+        <is>
+          <t>NAD / State Technical Board</t>
+        </is>
+      </c>
+      <c r="I83" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 15MB)</t>
+        </is>
+      </c>
+      <c r="J83" s="24" t="inlineStr">
+        <is>
+          <t>Consolidated_Marksheet_AllSem.pdf</t>
+        </is>
+      </c>
+      <c r="K83" s="24" t="inlineStr">
+        <is>
+          <t>Cumulative academic performance verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C84" s="28" t="inlineStr">
+        <is>
+          <t>Higher Secondary (12th / 10+2) Marksheet</t>
+        </is>
+      </c>
+      <c r="D84" s="27" t="inlineStr">
+        <is>
+          <t>docHsc12thMarksheet</t>
+        </is>
+      </c>
+      <c r="E84" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F84" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G84" s="27" t="inlineStr">
+        <is>
+          <t>School Education Board Verification</t>
+        </is>
+      </c>
+      <c r="H84" s="27" t="inlineStr">
+        <is>
+          <t>State / CBSE Education Board</t>
+        </is>
+      </c>
+      <c r="I84" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J84" s="27" t="inlineStr">
+        <is>
+          <t>HSC_12th_Marksheet.pdf</t>
+        </is>
+      </c>
+      <c r="K84" s="27" t="inlineStr">
+        <is>
+          <t>Intermediate secondary education record</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="23" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C85" s="25" t="inlineStr">
+        <is>
+          <t>SSLC (10th Standard) Marksheet / DOB Proof</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>docSslc10thMarksheet</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>Proof of Age / Factories Act Section 67</t>
+        </is>
+      </c>
+      <c r="H85" s="24" t="inlineStr">
+        <is>
+          <t>State Secondary Board</t>
+        </is>
+      </c>
+      <c r="I85" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J85" s="24" t="inlineStr">
+        <is>
+          <t>SSLC_10th_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K85" s="24" t="inlineStr">
+        <is>
+          <t>Statutory age &amp; date of birth authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C86" s="28" t="inlineStr">
+        <is>
+          <t>Previous Employer Official Relieving Letter</t>
+        </is>
+      </c>
+      <c r="D86" s="27" t="inlineStr">
+        <is>
+          <t>docRelievingLetter</t>
+        </is>
+      </c>
+      <c r="E86" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F86" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G86" s="27" t="inlineStr">
+        <is>
+          <t>Employment Separation &amp; Formal Exit</t>
+        </is>
+      </c>
+      <c r="H86" s="27" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust EPFO Service Passbook</t>
+        </is>
+      </c>
+      <c r="I86" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J86" s="27" t="inlineStr">
+        <is>
+          <t>Infosys_Relieving_Letter.pdf</t>
+        </is>
+      </c>
+      <c r="K86" s="27" t="inlineStr">
+        <is>
+          <t>Honorable exit and separation verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="23" t="n">
+        <v>83</v>
+      </c>
+      <c r="B87" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C87" s="25" t="inlineStr">
+        <is>
+          <t>Previous Service / Experience Certificate</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="inlineStr">
+        <is>
+          <t>docExperienceCertificate</t>
+        </is>
+      </c>
+      <c r="E87" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G87" s="24" t="inlineStr">
+        <is>
+          <t>Service Experience &amp; Band Hierarchy</t>
+        </is>
+      </c>
+      <c r="H87" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust EPFO &amp; HR Verification</t>
+        </is>
+      </c>
+      <c r="I87" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J87" s="24" t="inlineStr">
+        <is>
+          <t>Service_Experience_Letter.pdf</t>
+        </is>
+      </c>
+      <c r="K87" s="24" t="inlineStr">
+        <is>
+          <t>Past tenure &amp; role comparability audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="B88" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C88" s="28" t="inlineStr">
+        <is>
+          <t>Last 3 Months Consecutive Salary Slips</t>
+        </is>
+      </c>
+      <c r="D88" s="27" t="inlineStr">
+        <is>
+          <t>docSalarySlips3Months</t>
+        </is>
+      </c>
+      <c r="E88" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F88" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G88" s="27" t="inlineStr">
+        <is>
+          <t>Compensation &amp; Income Tax Form 16</t>
+        </is>
+      </c>
+      <c r="H88" s="27" t="inlineStr">
+        <is>
+          <t>Bank Payroll Deposit Matching</t>
+        </is>
+      </c>
+      <c r="I88" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 15MB)</t>
+        </is>
+      </c>
+      <c r="J88" s="27" t="inlineStr">
+        <is>
+          <t>Payslips_Last_3_Months.pdf</t>
+        </is>
+      </c>
+      <c r="K88" s="27" t="inlineStr">
+        <is>
+          <t>Last drawn CTC benchmarking &amp; tax continuity</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="23" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C89" s="25" t="inlineStr">
+        <is>
+          <t>Bank Pre-Printed Cancelled Cheque / Passbook</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="inlineStr">
+        <is>
+          <t>docBankCancelledCheque</t>
+        </is>
+      </c>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G89" s="24" t="inlineStr">
+        <is>
+          <t>Payment of Wages Act 1936 / Direct Credit</t>
+        </is>
+      </c>
+      <c r="H89" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust NPCI IMPS Penny Drop</t>
+        </is>
+      </c>
+      <c r="I89" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG, PNG (Showing Name &amp; IFSC)</t>
+        </is>
+      </c>
+      <c r="J89" s="24" t="inlineStr">
+        <is>
+          <t>HDFC_Cancelled_Cheque.jpg</t>
+        </is>
+      </c>
+      <c r="K89" s="24" t="inlineStr">
+        <is>
+          <t>Penny drop verified salary account proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C90" s="28" t="inlineStr">
+        <is>
+          <t>Previous Employer Form 16 / Tax Statement</t>
+        </is>
+      </c>
+      <c r="D90" s="27" t="inlineStr">
+        <is>
+          <t>docForm16TaxStatement</t>
+        </is>
+      </c>
+      <c r="E90" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F90" s="26" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="G90" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Act 1961 Section 203</t>
+        </is>
+      </c>
+      <c r="H90" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Traces Portal</t>
+        </is>
+      </c>
+      <c r="I90" s="27" t="inlineStr">
+        <is>
+          <t>PDF (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J90" s="27" t="inlineStr">
+        <is>
+          <t>Form16_PartA_PartB.pdf</t>
+        </is>
+      </c>
+      <c r="K90" s="27" t="inlineStr">
+        <is>
+          <t>TDS calculation &amp; mid-year tax continuity</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="23" t="n">
+        <v>87</v>
+      </c>
+      <c r="B91" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C91" s="25" t="inlineStr">
+        <is>
+          <t>Pre-Employment Medical Fitness Certificate</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="inlineStr">
+        <is>
+          <t>docMedicalFitnessCert</t>
+        </is>
+      </c>
+      <c r="E91" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G91" s="24" t="inlineStr">
+        <is>
+          <t>Occupational Health &amp; Group Insurance</t>
+        </is>
+      </c>
+      <c r="H91" s="24" t="inlineStr">
+        <is>
+          <t>Hospital / Registered Medical Practitioner</t>
+        </is>
+      </c>
+      <c r="I91" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J91" s="24" t="inlineStr">
+        <is>
+          <t>Medical_Fitness_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K91" s="24" t="inlineStr">
+        <is>
+          <t>Workplace physical fitness &amp; health insurance underwriting</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C92" s="28" t="inlineStr">
+        <is>
+          <t>Executed Non-Disclosure Agreement (NDA)</t>
+        </is>
+      </c>
+      <c r="D92" s="27" t="inlineStr">
+        <is>
+          <t>docSignedNda</t>
+        </is>
+      </c>
+      <c r="E92" s="27" t="inlineStr">
+        <is>
+          <t>File Upload / Checkbox Agreement</t>
+        </is>
+      </c>
+      <c r="F92" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G92" s="27" t="inlineStr">
+        <is>
+          <t>Indian Contract Act / Trade Secrets Protection</t>
+        </is>
+      </c>
+      <c r="H92" s="27" t="inlineStr">
+        <is>
+          <t>Internal Legal Compliance Hash</t>
+        </is>
+      </c>
+      <c r="I92" s="27" t="inlineStr">
+        <is>
+          <t>PDF / Digital Timestamp</t>
+        </is>
+      </c>
+      <c r="J92" s="27" t="inlineStr">
+        <is>
+          <t>Signed_NDA_IP_Assignment.pdf</t>
+        </is>
+      </c>
+      <c r="K92" s="27" t="inlineStr">
+        <is>
+          <t>Corporate confidentiality &amp; IP assignment execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="23" t="n">
+        <v>89</v>
+      </c>
+      <c r="B93" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C93" s="25" t="inlineStr">
+        <is>
+          <t>Commercial Heavy Vehicle Driving License (HMV)</t>
+        </is>
+      </c>
+      <c r="D93" s="24" t="inlineStr">
+        <is>
+          <t>docCommercialDl</t>
+        </is>
+      </c>
+      <c r="E93" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F93" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G93" s="24" t="inlineStr">
+        <is>
+          <t>Motor Vehicles Act 1988 / MoRTH Form 7</t>
+        </is>
+      </c>
+      <c r="H93" s="24" t="inlineStr">
         <is>
           <t>CoinCircleTrust MoRTH Sarathi API</t>
         </is>
       </c>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>15-16 alphanumeric</t>
-        </is>
-      </c>
-      <c r="J77" s="10" t="inlineStr">
-        <is>
-          <t>KA0120200004910</t>
-        </is>
-      </c>
-      <c r="K77" s="10" t="inlineStr">
-        <is>
-          <t>Commercial driving authorization</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="21" customHeight="1">
-      <c r="A78" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="B78" s="22" t="inlineStr">
+      <c r="I93" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Commercial Badge Visible)</t>
+        </is>
+      </c>
+      <c r="J93" s="24" t="inlineStr">
+        <is>
+          <t>Commercial_HMV_License.pdf</t>
+        </is>
+      </c>
+      <c r="K93" s="24" t="inlineStr">
+        <is>
+          <t>Heavy transport vehicle authorized driver check</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="26" t="n">
+        <v>90</v>
+      </c>
+      <c r="B94" s="27" t="inlineStr">
         <is>
           <t>11. Document Uploads &amp; Proofs</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>Vehicle RC Number &amp; Traffic Challan Search</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>assignedVehicleRc</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>Text Input</t>
-        </is>
-      </c>
-      <c r="F78" s="14" t="inlineStr">
+      <c r="C94" s="28" t="inlineStr">
+        <is>
+          <t>Vehicle Registration (RC Book) Copy</t>
+        </is>
+      </c>
+      <c r="D94" s="27" t="inlineStr">
+        <is>
+          <t>docVehicleRc</t>
+        </is>
+      </c>
+      <c r="E94" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F94" s="26" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="G78" s="10" t="inlineStr">
-        <is>
-          <t>Vahan National Vehicle Registry</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>CoinCircleTrust RC Advance API</t>
-        </is>
-      </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>10-digit vehicle RC</t>
-        </is>
-      </c>
-      <c r="J78" s="10" t="inlineStr">
-        <is>
-          <t>KA01MF4912</t>
-        </is>
-      </c>
-      <c r="K78" s="10" t="inlineStr">
-        <is>
-          <t>Vehicle registration audit</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="21" customHeight="1">
-      <c r="A79" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="B79" s="22" t="inlineStr">
+      <c r="G94" s="27" t="inlineStr">
+        <is>
+          <t>MoRTH Vahan 4.0 National Vehicle Registry</t>
+        </is>
+      </c>
+      <c r="H94" s="27" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust Vahan API</t>
+        </is>
+      </c>
+      <c r="I94" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J94" s="27" t="inlineStr">
+        <is>
+          <t>Vehicle_RC_Book.pdf</t>
+        </is>
+      </c>
+      <c r="K94" s="27" t="inlineStr">
+        <is>
+          <t>Vehicle fitness, roadworthiness &amp; insurance validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="23" t="n">
+        <v>91</v>
+      </c>
+      <c r="B95" s="24" t="inlineStr">
         <is>
           <t>11. Document Uploads &amp; Proofs</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C95" s="25" t="inlineStr">
         <is>
           <t>Vision &amp; Night Blindness Medical Certificate (Form 1A)</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>visionMedicalCert</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>File Upload</t>
-        </is>
-      </c>
-      <c r="F79" s="9" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="G79" s="10" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Act Section 8</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>Authorized Medical Practitioner</t>
-        </is>
-      </c>
-      <c r="I79" s="10" t="inlineStr">
-        <is>
-          <t>PDF File &lt; 5MB</t>
-        </is>
-      </c>
-      <c r="J79" s="10" t="inlineStr">
-        <is>
-          <t>Form1A_Vision_Report.pdf</t>
-        </is>
-      </c>
-      <c r="K79" s="10" t="inlineStr">
-        <is>
-          <t>Night vision and color distinction safety</t>
+      <c r="D95" s="24" t="inlineStr">
+        <is>
+          <t>docVisionForm1A</t>
+        </is>
+      </c>
+      <c r="E95" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F95" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G95" s="24" t="inlineStr">
+        <is>
+          <t>Motor Vehicles Act Section 8 / Form 1A</t>
+        </is>
+      </c>
+      <c r="H95" s="24" t="inlineStr">
+        <is>
+          <t>Ophthalmologist Medical Council</t>
+        </is>
+      </c>
+      <c r="I95" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J95" s="24" t="inlineStr">
+        <is>
+          <t>Form1A_Vision_Fitness.pdf</t>
+        </is>
+      </c>
+      <c r="K95" s="24" t="inlineStr">
+        <is>
+          <t>Night driving visual acuity &amp; color blindness clearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="26" t="n">
+        <v>92</v>
+      </c>
+      <c r="B96" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C96" s="28" t="inlineStr">
+        <is>
+          <t>Fleet GPS Telemetry &amp; Route Safety Policy</t>
+        </is>
+      </c>
+      <c r="D96" s="27" t="inlineStr">
+        <is>
+          <t>docGpsTelemetryConsent</t>
+        </is>
+      </c>
+      <c r="E96" s="27" t="inlineStr">
+        <is>
+          <t>Checkbox Agreement</t>
+        </is>
+      </c>
+      <c r="F96" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G96" s="27" t="inlineStr">
+        <is>
+          <t>AIS-140 Vehicle Tracking &amp; Fleet Policy</t>
+        </is>
+      </c>
+      <c r="H96" s="27" t="inlineStr">
+        <is>
+          <t>Logistics Dispatch Telemetry</t>
+        </is>
+      </c>
+      <c r="I96" s="27" t="inlineStr">
+        <is>
+          <t>Digital Agreement Checkbox</t>
+        </is>
+      </c>
+      <c r="J96" s="27" t="inlineStr">
+        <is>
+          <t>True (Agreed &amp; Executed)</t>
+        </is>
+      </c>
+      <c r="K96" s="27" t="inlineStr">
+        <is>
+          <t>Real-time GPS route tracking &amp; safe driving compliance</t>
         </is>
       </c>
     </row>
@@ -17129,8 +20808,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K96"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -21063,167 +24742,1102 @@
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="22" t="inlineStr">
+      <c r="B77" s="24" t="inlineStr">
         <is>
           <t>11. Document Uploads &amp; Proofs</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>Medical / Nursing Council Registration Number</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>councilRegNumber</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>Text Input</t>
-        </is>
-      </c>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="G77" s="10" t="inlineStr">
-        <is>
-          <t>National Medical Commission Act 2019</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>State Medical Council Portal</t>
-        </is>
-      </c>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>Registration Number</t>
-        </is>
-      </c>
-      <c r="J77" s="10" t="inlineStr">
-        <is>
-          <t>KMC-REG-2012-9942</t>
-        </is>
-      </c>
-      <c r="K77" s="10" t="inlineStr">
-        <is>
-          <t>Mandatory statutory license to practice</t>
+      <c r="C77" s="25" t="inlineStr">
+        <is>
+          <t>Government Aadhaar Card (Front &amp; Back)</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr">
+        <is>
+          <t>docAadhaar</t>
+        </is>
+      </c>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F77" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G77" s="24" t="inlineStr">
+        <is>
+          <t>Aadhaar Act 2016 / Sovereign Identity</t>
+        </is>
+      </c>
+      <c r="H77" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust UIDAI e-KYC / OCR</t>
+        </is>
+      </c>
+      <c r="I77" s="24" t="inlineStr">
+        <is>
+          <t>PDF, PNG, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J77" s="24" t="inlineStr">
+        <is>
+          <t>Aadhaar_Card_Masked.pdf</t>
+        </is>
+      </c>
+      <c r="K77" s="24" t="inlineStr">
+        <is>
+          <t>Primary sovereign identity &amp; age proof</t>
         </is>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
-      <c r="A78" s="5" t="n">
+      <c r="A78" s="26" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="22" t="inlineStr">
+      <c r="B78" s="27" t="inlineStr">
         <is>
           <t>11. Document Uploads &amp; Proofs</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>Life Support Certifications (BLS / ACLS)</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>lifeSupportCert</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>Dropdown Select</t>
-        </is>
-      </c>
-      <c r="F78" s="9" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="G78" s="10" t="inlineStr">
-        <is>
-          <t>NABH / JCI Hospital Accreditation</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>American Heart Association (AHA)</t>
-        </is>
-      </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>BLS Certified | ACLS Certified</t>
-        </is>
-      </c>
-      <c r="J78" s="10" t="inlineStr">
-        <is>
-          <t>BLS &amp; ACLS Certified</t>
-        </is>
-      </c>
-      <c r="K78" s="10" t="inlineStr">
-        <is>
-          <t>Critical care emergency life support clearance</t>
+      <c r="C78" s="28" t="inlineStr">
+        <is>
+          <t>Income Tax PAN Card Copy</t>
+        </is>
+      </c>
+      <c r="D78" s="27" t="inlineStr">
+        <is>
+          <t>docPan</t>
+        </is>
+      </c>
+      <c r="E78" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F78" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G78" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Act 1961 / Form 16</t>
+        </is>
+      </c>
+      <c r="H78" s="27" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust NSDL PAN Verification</t>
+        </is>
+      </c>
+      <c r="I78" s="27" t="inlineStr">
+        <is>
+          <t>PDF, PNG, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J78" s="27" t="inlineStr">
+        <is>
+          <t>PAN_Card_Color_Scan.jpg</t>
+        </is>
+      </c>
+      <c r="K78" s="27" t="inlineStr">
+        <is>
+          <t>Statutory tax deduction &amp; TAN linkage</t>
         </is>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
-      <c r="A79" s="5" t="n">
+      <c r="A79" s="23" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="22" t="inlineStr">
+      <c r="B79" s="24" t="inlineStr">
         <is>
           <t>11. Document Uploads &amp; Proofs</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C79" s="25" t="inlineStr">
+        <is>
+          <t>Formal Passport Size Photograph</t>
+        </is>
+      </c>
+      <c r="D79" s="24" t="inlineStr">
+        <is>
+          <t>docPassportPhoto</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>File Upload / Live Photo Capture</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G79" s="24" t="inlineStr">
+        <is>
+          <t>Corporate ID Badge / Labor Welfare Form</t>
+        </is>
+      </c>
+      <c r="H79" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust AI Face Biometrics</t>
+        </is>
+      </c>
+      <c r="I79" s="24" t="inlineStr">
+        <is>
+          <t>JPG, PNG (White Background, Max 5MB)</t>
+        </is>
+      </c>
+      <c r="J79" s="24" t="inlineStr">
+        <is>
+          <t>Employee_Formal_Photo.jpg</t>
+        </is>
+      </c>
+      <c r="K79" s="24" t="inlineStr">
+        <is>
+          <t>Employee ID card &amp; face biometric record</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="26" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C80" s="28" t="inlineStr">
+        <is>
+          <t>Official Specimen Signature on Paper</t>
+        </is>
+      </c>
+      <c r="D80" s="27" t="inlineStr">
+        <is>
+          <t>docSpecimenSignature</t>
+        </is>
+      </c>
+      <c r="E80" s="27" t="inlineStr">
+        <is>
+          <t>File Upload / Digital Canvas</t>
+        </is>
+      </c>
+      <c r="F80" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G80" s="27" t="inlineStr">
+        <is>
+          <t>Indian Contract Act 1872 / Form F Gratuity</t>
+        </is>
+      </c>
+      <c r="H80" s="27" t="inlineStr">
+        <is>
+          <t>Internal Audit Vault Signature</t>
+        </is>
+      </c>
+      <c r="I80" s="27" t="inlineStr">
+        <is>
+          <t>PNG, JPG (Clear Signature, Max 2MB)</t>
+        </is>
+      </c>
+      <c r="J80" s="27" t="inlineStr">
+        <is>
+          <t>Specimen_Signature_Sample.png</t>
+        </is>
+      </c>
+      <c r="K80" s="27" t="inlineStr">
+        <is>
+          <t>Statutory nomination &amp; bank payroll execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="23" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C81" s="25" t="inlineStr">
+        <is>
+          <t>Passport / Driving License / Voter ID</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="inlineStr">
+        <is>
+          <t>docPassportOrDl</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G81" s="24" t="inlineStr">
+        <is>
+          <t>Secondary Sovereign ID / MoRTH / MEA</t>
+        </is>
+      </c>
+      <c r="H81" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust MoRTH / MEA Gateway</t>
+        </is>
+      </c>
+      <c r="I81" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J81" s="24" t="inlineStr">
+        <is>
+          <t>Passport_First_Last_Page.pdf</t>
+        </is>
+      </c>
+      <c r="K81" s="24" t="inlineStr">
+        <is>
+          <t>Secondary identity &amp; international travel readiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="26" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C82" s="28" t="inlineStr">
+        <is>
+          <t>Highest Degree / Convocation Certificate</t>
+        </is>
+      </c>
+      <c r="D82" s="27" t="inlineStr">
+        <is>
+          <t>docDegreeCert</t>
+        </is>
+      </c>
+      <c r="E82" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F82" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G82" s="27" t="inlineStr">
+        <is>
+          <t>Academic Qualifications &amp; Skill Audit</t>
+        </is>
+      </c>
+      <c r="H82" s="27" t="inlineStr">
+        <is>
+          <t>National Academic Depository (NAD) / University</t>
+        </is>
+      </c>
+      <c r="I82" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J82" s="27" t="inlineStr">
+        <is>
+          <t>BTech_Degree_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K82" s="27" t="inlineStr">
+        <is>
+          <t>Highest qualification credential authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="23" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C83" s="25" t="inlineStr">
+        <is>
+          <t>Consolidated / All Semester Marksheets</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr">
+        <is>
+          <t>docConsolidatedMarksheet</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F83" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="inlineStr">
+        <is>
+          <t>Academic Score &amp; Integrity Check</t>
+        </is>
+      </c>
+      <c r="H83" s="24" t="inlineStr">
+        <is>
+          <t>NAD / State Technical Board</t>
+        </is>
+      </c>
+      <c r="I83" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 15MB)</t>
+        </is>
+      </c>
+      <c r="J83" s="24" t="inlineStr">
+        <is>
+          <t>Consolidated_Marksheet_AllSem.pdf</t>
+        </is>
+      </c>
+      <c r="K83" s="24" t="inlineStr">
+        <is>
+          <t>Cumulative academic performance verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C84" s="28" t="inlineStr">
+        <is>
+          <t>Higher Secondary (12th / 10+2) Marksheet</t>
+        </is>
+      </c>
+      <c r="D84" s="27" t="inlineStr">
+        <is>
+          <t>docHsc12thMarksheet</t>
+        </is>
+      </c>
+      <c r="E84" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F84" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G84" s="27" t="inlineStr">
+        <is>
+          <t>School Education Board Verification</t>
+        </is>
+      </c>
+      <c r="H84" s="27" t="inlineStr">
+        <is>
+          <t>State / CBSE Education Board</t>
+        </is>
+      </c>
+      <c r="I84" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J84" s="27" t="inlineStr">
+        <is>
+          <t>HSC_12th_Marksheet.pdf</t>
+        </is>
+      </c>
+      <c r="K84" s="27" t="inlineStr">
+        <is>
+          <t>Intermediate secondary education record</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="23" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C85" s="25" t="inlineStr">
+        <is>
+          <t>SSLC (10th Standard) Marksheet / DOB Proof</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>docSslc10thMarksheet</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>Proof of Age / Factories Act Section 67</t>
+        </is>
+      </c>
+      <c r="H85" s="24" t="inlineStr">
+        <is>
+          <t>State Secondary Board</t>
+        </is>
+      </c>
+      <c r="I85" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J85" s="24" t="inlineStr">
+        <is>
+          <t>SSLC_10th_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K85" s="24" t="inlineStr">
+        <is>
+          <t>Statutory age &amp; date of birth authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C86" s="28" t="inlineStr">
+        <is>
+          <t>Previous Employer Official Relieving Letter</t>
+        </is>
+      </c>
+      <c r="D86" s="27" t="inlineStr">
+        <is>
+          <t>docRelievingLetter</t>
+        </is>
+      </c>
+      <c r="E86" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F86" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G86" s="27" t="inlineStr">
+        <is>
+          <t>Employment Separation &amp; Formal Exit</t>
+        </is>
+      </c>
+      <c r="H86" s="27" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust EPFO Service Passbook</t>
+        </is>
+      </c>
+      <c r="I86" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J86" s="27" t="inlineStr">
+        <is>
+          <t>Infosys_Relieving_Letter.pdf</t>
+        </is>
+      </c>
+      <c r="K86" s="27" t="inlineStr">
+        <is>
+          <t>Honorable exit and separation verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="23" t="n">
+        <v>83</v>
+      </c>
+      <c r="B87" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C87" s="25" t="inlineStr">
+        <is>
+          <t>Previous Service / Experience Certificate</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="inlineStr">
+        <is>
+          <t>docExperienceCertificate</t>
+        </is>
+      </c>
+      <c r="E87" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G87" s="24" t="inlineStr">
+        <is>
+          <t>Service Experience &amp; Band Hierarchy</t>
+        </is>
+      </c>
+      <c r="H87" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust EPFO &amp; HR Verification</t>
+        </is>
+      </c>
+      <c r="I87" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J87" s="24" t="inlineStr">
+        <is>
+          <t>Service_Experience_Letter.pdf</t>
+        </is>
+      </c>
+      <c r="K87" s="24" t="inlineStr">
+        <is>
+          <t>Past tenure &amp; role comparability audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="B88" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C88" s="28" t="inlineStr">
+        <is>
+          <t>Last 3 Months Consecutive Salary Slips</t>
+        </is>
+      </c>
+      <c r="D88" s="27" t="inlineStr">
+        <is>
+          <t>docSalarySlips3Months</t>
+        </is>
+      </c>
+      <c r="E88" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F88" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G88" s="27" t="inlineStr">
+        <is>
+          <t>Compensation &amp; Income Tax Form 16</t>
+        </is>
+      </c>
+      <c r="H88" s="27" t="inlineStr">
+        <is>
+          <t>Bank Payroll Deposit Matching</t>
+        </is>
+      </c>
+      <c r="I88" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 15MB)</t>
+        </is>
+      </c>
+      <c r="J88" s="27" t="inlineStr">
+        <is>
+          <t>Payslips_Last_3_Months.pdf</t>
+        </is>
+      </c>
+      <c r="K88" s="27" t="inlineStr">
+        <is>
+          <t>Last drawn CTC benchmarking &amp; tax continuity</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="23" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C89" s="25" t="inlineStr">
+        <is>
+          <t>Bank Pre-Printed Cancelled Cheque / Passbook</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="inlineStr">
+        <is>
+          <t>docBankCancelledCheque</t>
+        </is>
+      </c>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G89" s="24" t="inlineStr">
+        <is>
+          <t>Payment of Wages Act 1936 / Direct Credit</t>
+        </is>
+      </c>
+      <c r="H89" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust NPCI IMPS Penny Drop</t>
+        </is>
+      </c>
+      <c r="I89" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG, PNG (Showing Name &amp; IFSC)</t>
+        </is>
+      </c>
+      <c r="J89" s="24" t="inlineStr">
+        <is>
+          <t>HDFC_Cancelled_Cheque.jpg</t>
+        </is>
+      </c>
+      <c r="K89" s="24" t="inlineStr">
+        <is>
+          <t>Penny drop verified salary account proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C90" s="28" t="inlineStr">
+        <is>
+          <t>Previous Employer Form 16 / Tax Statement</t>
+        </is>
+      </c>
+      <c r="D90" s="27" t="inlineStr">
+        <is>
+          <t>docForm16TaxStatement</t>
+        </is>
+      </c>
+      <c r="E90" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F90" s="26" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="G90" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Act 1961 Section 203</t>
+        </is>
+      </c>
+      <c r="H90" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Traces Portal</t>
+        </is>
+      </c>
+      <c r="I90" s="27" t="inlineStr">
+        <is>
+          <t>PDF (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J90" s="27" t="inlineStr">
+        <is>
+          <t>Form16_PartA_PartB.pdf</t>
+        </is>
+      </c>
+      <c r="K90" s="27" t="inlineStr">
+        <is>
+          <t>TDS calculation &amp; mid-year tax continuity</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="23" t="n">
+        <v>87</v>
+      </c>
+      <c r="B91" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C91" s="25" t="inlineStr">
+        <is>
+          <t>Pre-Employment Medical Fitness Certificate</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="inlineStr">
+        <is>
+          <t>docMedicalFitnessCert</t>
+        </is>
+      </c>
+      <c r="E91" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G91" s="24" t="inlineStr">
+        <is>
+          <t>Occupational Health &amp; Group Insurance</t>
+        </is>
+      </c>
+      <c r="H91" s="24" t="inlineStr">
+        <is>
+          <t>Hospital / Registered Medical Practitioner</t>
+        </is>
+      </c>
+      <c r="I91" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J91" s="24" t="inlineStr">
+        <is>
+          <t>Medical_Fitness_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K91" s="24" t="inlineStr">
+        <is>
+          <t>Workplace physical fitness &amp; health insurance underwriting</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C92" s="28" t="inlineStr">
+        <is>
+          <t>Executed Non-Disclosure Agreement (NDA)</t>
+        </is>
+      </c>
+      <c r="D92" s="27" t="inlineStr">
+        <is>
+          <t>docSignedNda</t>
+        </is>
+      </c>
+      <c r="E92" s="27" t="inlineStr">
+        <is>
+          <t>File Upload / Checkbox Agreement</t>
+        </is>
+      </c>
+      <c r="F92" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G92" s="27" t="inlineStr">
+        <is>
+          <t>Indian Contract Act / Trade Secrets Protection</t>
+        </is>
+      </c>
+      <c r="H92" s="27" t="inlineStr">
+        <is>
+          <t>Internal Legal Compliance Hash</t>
+        </is>
+      </c>
+      <c r="I92" s="27" t="inlineStr">
+        <is>
+          <t>PDF / Digital Timestamp</t>
+        </is>
+      </c>
+      <c r="J92" s="27" t="inlineStr">
+        <is>
+          <t>Signed_NDA_IP_Assignment.pdf</t>
+        </is>
+      </c>
+      <c r="K92" s="27" t="inlineStr">
+        <is>
+          <t>Corporate confidentiality &amp; IP assignment execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="23" t="n">
+        <v>89</v>
+      </c>
+      <c r="B93" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C93" s="25" t="inlineStr">
+        <is>
+          <t>Medical / Nursing / Pharmacy Council Registration</t>
+        </is>
+      </c>
+      <c r="D93" s="24" t="inlineStr">
+        <is>
+          <t>docCouncilReg</t>
+        </is>
+      </c>
+      <c r="E93" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F93" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G93" s="24" t="inlineStr">
+        <is>
+          <t>National Medical Commission / State Nursing Council</t>
+        </is>
+      </c>
+      <c r="H93" s="24" t="inlineStr">
+        <is>
+          <t>NMC / State Professional Registry</t>
+        </is>
+      </c>
+      <c r="I93" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Registration Badge Visible)</t>
+        </is>
+      </c>
+      <c r="J93" s="24" t="inlineStr">
+        <is>
+          <t>Medical_Council_Registration.pdf</t>
+        </is>
+      </c>
+      <c r="K93" s="24" t="inlineStr">
+        <is>
+          <t>Statutory healthcare license &amp; credential authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="26" t="n">
+        <v>90</v>
+      </c>
+      <c r="B94" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C94" s="28" t="inlineStr">
+        <is>
+          <t>Basic Life Support (BLS / ACLS) Certification</t>
+        </is>
+      </c>
+      <c r="D94" s="27" t="inlineStr">
+        <is>
+          <t>docLifeSupportCert</t>
+        </is>
+      </c>
+      <c r="E94" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F94" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G94" s="27" t="inlineStr">
+        <is>
+          <t>NABH / JCI Hospital Accreditation Norms</t>
+        </is>
+      </c>
+      <c r="H94" s="27" t="inlineStr">
+        <is>
+          <t>American Heart Association / ERC Registry</t>
+        </is>
+      </c>
+      <c r="I94" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Valid Expiry Date)</t>
+        </is>
+      </c>
+      <c r="J94" s="27" t="inlineStr">
+        <is>
+          <t>AHA_BLS_ACLS_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K94" s="27" t="inlineStr">
+        <is>
+          <t>Critical care life support emergency readiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="23" t="n">
+        <v>91</v>
+      </c>
+      <c r="B95" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C95" s="25" t="inlineStr">
         <is>
           <t>Hepatitis B &amp; Tetanus Vaccination Record</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>vaccinationRecord</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>File Upload</t>
-        </is>
-      </c>
-      <c r="F79" s="9" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="G79" s="10" t="inlineStr">
-        <is>
-          <t>Hospital Infection Control &amp; CDC</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>Occupational Health Screening</t>
-        </is>
-      </c>
-      <c r="I79" s="10" t="inlineStr">
-        <is>
-          <t>PDF File &lt; 5MB</t>
-        </is>
-      </c>
-      <c r="J79" s="10" t="inlineStr">
-        <is>
-          <t>HepB_Titer_Report.pdf</t>
-        </is>
-      </c>
-      <c r="K79" s="10" t="inlineStr">
-        <is>
-          <t>Immunity against blood-borne occupational pathogens</t>
+      <c r="D95" s="24" t="inlineStr">
+        <is>
+          <t>docVaccinationRecord</t>
+        </is>
+      </c>
+      <c r="E95" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F95" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G95" s="24" t="inlineStr">
+        <is>
+          <t>Hospital Infection Control &amp; CDC Guidelines</t>
+        </is>
+      </c>
+      <c r="H95" s="24" t="inlineStr">
+        <is>
+          <t>Hospital Occupational Health Registry</t>
+        </is>
+      </c>
+      <c r="I95" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Showing 3 Doses)</t>
+        </is>
+      </c>
+      <c r="J95" s="24" t="inlineStr">
+        <is>
+          <t>Immunization_Vaccination_Card.pdf</t>
+        </is>
+      </c>
+      <c r="K95" s="24" t="inlineStr">
+        <is>
+          <t>Patient safety &amp; occupational biohazard protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="26" t="n">
+        <v>92</v>
+      </c>
+      <c r="B96" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C96" s="28" t="inlineStr">
+        <is>
+          <t>NABH / GMP Cleanroom &amp; Bio-Safety Undertaking</t>
+        </is>
+      </c>
+      <c r="D96" s="27" t="inlineStr">
+        <is>
+          <t>docCleanroomGmpProtocol</t>
+        </is>
+      </c>
+      <c r="E96" s="27" t="inlineStr">
+        <is>
+          <t>Checkbox Agreement</t>
+        </is>
+      </c>
+      <c r="F96" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G96" s="27" t="inlineStr">
+        <is>
+          <t>Drugs &amp; Cosmetics Act 1940 / Schedule M (GMP)</t>
+        </is>
+      </c>
+      <c r="H96" s="27" t="inlineStr">
+        <is>
+          <t>Hospital Clinical Governance Hash</t>
+        </is>
+      </c>
+      <c r="I96" s="27" t="inlineStr">
+        <is>
+          <t>Digital Agreement Checkbox</t>
+        </is>
+      </c>
+      <c r="J96" s="27" t="inlineStr">
+        <is>
+          <t>True (Agreed &amp; Signed)</t>
+        </is>
+      </c>
+      <c r="K96" s="27" t="inlineStr">
+        <is>
+          <t>Cleanroom sterilization &amp; patient privacy adherence</t>
         </is>
       </c>
     </row>
@@ -21242,8 +25856,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K95"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -25176,112 +29790,1047 @@
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="22" t="inlineStr">
+      <c r="B77" s="24" t="inlineStr">
         <is>
           <t>11. Document Uploads &amp; Proofs</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>Two-Wheeler Driving License (DL) for Field Travel</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>fieldSalesDl</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>Text Input</t>
-        </is>
-      </c>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="G77" s="10" t="inlineStr">
-        <is>
-          <t>Field Travel Policy</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>CoinCircleTrust MoRTH DL API</t>
-        </is>
-      </c>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>DL Number</t>
-        </is>
-      </c>
-      <c r="J77" s="10" t="inlineStr">
-        <is>
-          <t>TN0120180004918</t>
-        </is>
-      </c>
-      <c r="K77" s="10" t="inlineStr">
-        <is>
-          <t>Validation of two-wheeler driving license for field travel</t>
+      <c r="C77" s="25" t="inlineStr">
+        <is>
+          <t>Government Aadhaar Card (Front &amp; Back)</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr">
+        <is>
+          <t>docAadhaar</t>
+        </is>
+      </c>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F77" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G77" s="24" t="inlineStr">
+        <is>
+          <t>Aadhaar Act 2016 / Sovereign Identity</t>
+        </is>
+      </c>
+      <c r="H77" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust UIDAI e-KYC / OCR</t>
+        </is>
+      </c>
+      <c r="I77" s="24" t="inlineStr">
+        <is>
+          <t>PDF, PNG, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J77" s="24" t="inlineStr">
+        <is>
+          <t>Aadhaar_Card_Masked.pdf</t>
+        </is>
+      </c>
+      <c r="K77" s="24" t="inlineStr">
+        <is>
+          <t>Primary sovereign identity &amp; age proof</t>
         </is>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
-      <c r="A78" s="5" t="n">
+      <c r="A78" s="26" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="22" t="inlineStr">
+      <c r="B78" s="27" t="inlineStr">
         <is>
           <t>11. Document Uploads &amp; Proofs</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>Cash Handling &amp; Store POS Policy Agreement</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>cashHandlingPolicy</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="C78" s="28" t="inlineStr">
+        <is>
+          <t>Income Tax PAN Card Copy</t>
+        </is>
+      </c>
+      <c r="D78" s="27" t="inlineStr">
+        <is>
+          <t>docPan</t>
+        </is>
+      </c>
+      <c r="E78" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F78" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G78" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Act 1961 / Form 16</t>
+        </is>
+      </c>
+      <c r="H78" s="27" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust NSDL PAN Verification</t>
+        </is>
+      </c>
+      <c r="I78" s="27" t="inlineStr">
+        <is>
+          <t>PDF, PNG, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J78" s="27" t="inlineStr">
+        <is>
+          <t>PAN_Card_Color_Scan.jpg</t>
+        </is>
+      </c>
+      <c r="K78" s="27" t="inlineStr">
+        <is>
+          <t>Statutory tax deduction &amp; TAN linkage</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="23" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C79" s="25" t="inlineStr">
+        <is>
+          <t>Formal Passport Size Photograph</t>
+        </is>
+      </c>
+      <c r="D79" s="24" t="inlineStr">
+        <is>
+          <t>docPassportPhoto</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>File Upload / Live Photo Capture</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G79" s="24" t="inlineStr">
+        <is>
+          <t>Corporate ID Badge / Labor Welfare Form</t>
+        </is>
+      </c>
+      <c r="H79" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust AI Face Biometrics</t>
+        </is>
+      </c>
+      <c r="I79" s="24" t="inlineStr">
+        <is>
+          <t>JPG, PNG (White Background, Max 5MB)</t>
+        </is>
+      </c>
+      <c r="J79" s="24" t="inlineStr">
+        <is>
+          <t>Employee_Formal_Photo.jpg</t>
+        </is>
+      </c>
+      <c r="K79" s="24" t="inlineStr">
+        <is>
+          <t>Employee ID card &amp; face biometric record</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="26" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C80" s="28" t="inlineStr">
+        <is>
+          <t>Official Specimen Signature on Paper</t>
+        </is>
+      </c>
+      <c r="D80" s="27" t="inlineStr">
+        <is>
+          <t>docSpecimenSignature</t>
+        </is>
+      </c>
+      <c r="E80" s="27" t="inlineStr">
+        <is>
+          <t>File Upload / Digital Canvas</t>
+        </is>
+      </c>
+      <c r="F80" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G80" s="27" t="inlineStr">
+        <is>
+          <t>Indian Contract Act 1872 / Form F Gratuity</t>
+        </is>
+      </c>
+      <c r="H80" s="27" t="inlineStr">
+        <is>
+          <t>Internal Audit Vault Signature</t>
+        </is>
+      </c>
+      <c r="I80" s="27" t="inlineStr">
+        <is>
+          <t>PNG, JPG (Clear Signature, Max 2MB)</t>
+        </is>
+      </c>
+      <c r="J80" s="27" t="inlineStr">
+        <is>
+          <t>Specimen_Signature_Sample.png</t>
+        </is>
+      </c>
+      <c r="K80" s="27" t="inlineStr">
+        <is>
+          <t>Statutory nomination &amp; bank payroll execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="23" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C81" s="25" t="inlineStr">
+        <is>
+          <t>Passport / Driving License / Voter ID</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="inlineStr">
+        <is>
+          <t>docPassportOrDl</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G81" s="24" t="inlineStr">
+        <is>
+          <t>Secondary Sovereign ID / MoRTH / MEA</t>
+        </is>
+      </c>
+      <c r="H81" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust MoRTH / MEA Gateway</t>
+        </is>
+      </c>
+      <c r="I81" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J81" s="24" t="inlineStr">
+        <is>
+          <t>Passport_First_Last_Page.pdf</t>
+        </is>
+      </c>
+      <c r="K81" s="24" t="inlineStr">
+        <is>
+          <t>Secondary identity &amp; international travel readiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="26" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C82" s="28" t="inlineStr">
+        <is>
+          <t>Highest Degree / Convocation Certificate</t>
+        </is>
+      </c>
+      <c r="D82" s="27" t="inlineStr">
+        <is>
+          <t>docDegreeCert</t>
+        </is>
+      </c>
+      <c r="E82" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F82" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G82" s="27" t="inlineStr">
+        <is>
+          <t>Academic Qualifications &amp; Skill Audit</t>
+        </is>
+      </c>
+      <c r="H82" s="27" t="inlineStr">
+        <is>
+          <t>National Academic Depository (NAD) / University</t>
+        </is>
+      </c>
+      <c r="I82" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J82" s="27" t="inlineStr">
+        <is>
+          <t>BTech_Degree_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K82" s="27" t="inlineStr">
+        <is>
+          <t>Highest qualification credential authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="23" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C83" s="25" t="inlineStr">
+        <is>
+          <t>Consolidated / All Semester Marksheets</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr">
+        <is>
+          <t>docConsolidatedMarksheet</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F83" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="inlineStr">
+        <is>
+          <t>Academic Score &amp; Integrity Check</t>
+        </is>
+      </c>
+      <c r="H83" s="24" t="inlineStr">
+        <is>
+          <t>NAD / State Technical Board</t>
+        </is>
+      </c>
+      <c r="I83" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 15MB)</t>
+        </is>
+      </c>
+      <c r="J83" s="24" t="inlineStr">
+        <is>
+          <t>Consolidated_Marksheet_AllSem.pdf</t>
+        </is>
+      </c>
+      <c r="K83" s="24" t="inlineStr">
+        <is>
+          <t>Cumulative academic performance verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C84" s="28" t="inlineStr">
+        <is>
+          <t>Higher Secondary (12th / 10+2) Marksheet</t>
+        </is>
+      </c>
+      <c r="D84" s="27" t="inlineStr">
+        <is>
+          <t>docHsc12thMarksheet</t>
+        </is>
+      </c>
+      <c r="E84" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F84" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G84" s="27" t="inlineStr">
+        <is>
+          <t>School Education Board Verification</t>
+        </is>
+      </c>
+      <c r="H84" s="27" t="inlineStr">
+        <is>
+          <t>State / CBSE Education Board</t>
+        </is>
+      </c>
+      <c r="I84" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J84" s="27" t="inlineStr">
+        <is>
+          <t>HSC_12th_Marksheet.pdf</t>
+        </is>
+      </c>
+      <c r="K84" s="27" t="inlineStr">
+        <is>
+          <t>Intermediate secondary education record</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="23" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C85" s="25" t="inlineStr">
+        <is>
+          <t>SSLC (10th Standard) Marksheet / DOB Proof</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>docSslc10thMarksheet</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>Proof of Age / Factories Act Section 67</t>
+        </is>
+      </c>
+      <c r="H85" s="24" t="inlineStr">
+        <is>
+          <t>State Secondary Board</t>
+        </is>
+      </c>
+      <c r="I85" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J85" s="24" t="inlineStr">
+        <is>
+          <t>SSLC_10th_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K85" s="24" t="inlineStr">
+        <is>
+          <t>Statutory age &amp; date of birth authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C86" s="28" t="inlineStr">
+        <is>
+          <t>Previous Employer Official Relieving Letter</t>
+        </is>
+      </c>
+      <c r="D86" s="27" t="inlineStr">
+        <is>
+          <t>docRelievingLetter</t>
+        </is>
+      </c>
+      <c r="E86" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F86" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G86" s="27" t="inlineStr">
+        <is>
+          <t>Employment Separation &amp; Formal Exit</t>
+        </is>
+      </c>
+      <c r="H86" s="27" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust EPFO Service Passbook</t>
+        </is>
+      </c>
+      <c r="I86" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J86" s="27" t="inlineStr">
+        <is>
+          <t>Infosys_Relieving_Letter.pdf</t>
+        </is>
+      </c>
+      <c r="K86" s="27" t="inlineStr">
+        <is>
+          <t>Honorable exit and separation verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="23" t="n">
+        <v>83</v>
+      </c>
+      <c r="B87" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C87" s="25" t="inlineStr">
+        <is>
+          <t>Previous Service / Experience Certificate</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="inlineStr">
+        <is>
+          <t>docExperienceCertificate</t>
+        </is>
+      </c>
+      <c r="E87" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G87" s="24" t="inlineStr">
+        <is>
+          <t>Service Experience &amp; Band Hierarchy</t>
+        </is>
+      </c>
+      <c r="H87" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust EPFO &amp; HR Verification</t>
+        </is>
+      </c>
+      <c r="I87" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J87" s="24" t="inlineStr">
+        <is>
+          <t>Service_Experience_Letter.pdf</t>
+        </is>
+      </c>
+      <c r="K87" s="24" t="inlineStr">
+        <is>
+          <t>Past tenure &amp; role comparability audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="B88" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C88" s="28" t="inlineStr">
+        <is>
+          <t>Last 3 Months Consecutive Salary Slips</t>
+        </is>
+      </c>
+      <c r="D88" s="27" t="inlineStr">
+        <is>
+          <t>docSalarySlips3Months</t>
+        </is>
+      </c>
+      <c r="E88" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F88" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G88" s="27" t="inlineStr">
+        <is>
+          <t>Compensation &amp; Income Tax Form 16</t>
+        </is>
+      </c>
+      <c r="H88" s="27" t="inlineStr">
+        <is>
+          <t>Bank Payroll Deposit Matching</t>
+        </is>
+      </c>
+      <c r="I88" s="27" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 15MB)</t>
+        </is>
+      </c>
+      <c r="J88" s="27" t="inlineStr">
+        <is>
+          <t>Payslips_Last_3_Months.pdf</t>
+        </is>
+      </c>
+      <c r="K88" s="27" t="inlineStr">
+        <is>
+          <t>Last drawn CTC benchmarking &amp; tax continuity</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="23" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C89" s="25" t="inlineStr">
+        <is>
+          <t>Bank Pre-Printed Cancelled Cheque / Passbook</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="inlineStr">
+        <is>
+          <t>docBankCancelledCheque</t>
+        </is>
+      </c>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G89" s="24" t="inlineStr">
+        <is>
+          <t>Payment of Wages Act 1936 / Direct Credit</t>
+        </is>
+      </c>
+      <c r="H89" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust NPCI IMPS Penny Drop</t>
+        </is>
+      </c>
+      <c r="I89" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG, PNG (Showing Name &amp; IFSC)</t>
+        </is>
+      </c>
+      <c r="J89" s="24" t="inlineStr">
+        <is>
+          <t>HDFC_Cancelled_Cheque.jpg</t>
+        </is>
+      </c>
+      <c r="K89" s="24" t="inlineStr">
+        <is>
+          <t>Penny drop verified salary account proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C90" s="28" t="inlineStr">
+        <is>
+          <t>Previous Employer Form 16 / Tax Statement</t>
+        </is>
+      </c>
+      <c r="D90" s="27" t="inlineStr">
+        <is>
+          <t>docForm16TaxStatement</t>
+        </is>
+      </c>
+      <c r="E90" s="27" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F90" s="26" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="G90" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Act 1961 Section 203</t>
+        </is>
+      </c>
+      <c r="H90" s="27" t="inlineStr">
+        <is>
+          <t>Income Tax Traces Portal</t>
+        </is>
+      </c>
+      <c r="I90" s="27" t="inlineStr">
+        <is>
+          <t>PDF (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J90" s="27" t="inlineStr">
+        <is>
+          <t>Form16_PartA_PartB.pdf</t>
+        </is>
+      </c>
+      <c r="K90" s="27" t="inlineStr">
+        <is>
+          <t>TDS calculation &amp; mid-year tax continuity</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="23" t="n">
+        <v>87</v>
+      </c>
+      <c r="B91" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C91" s="25" t="inlineStr">
+        <is>
+          <t>Pre-Employment Medical Fitness Certificate</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="inlineStr">
+        <is>
+          <t>docMedicalFitnessCert</t>
+        </is>
+      </c>
+      <c r="E91" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G91" s="24" t="inlineStr">
+        <is>
+          <t>Occupational Health &amp; Group Insurance</t>
+        </is>
+      </c>
+      <c r="H91" s="24" t="inlineStr">
+        <is>
+          <t>Hospital / Registered Medical Practitioner</t>
+        </is>
+      </c>
+      <c r="I91" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J91" s="24" t="inlineStr">
+        <is>
+          <t>Medical_Fitness_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K91" s="24" t="inlineStr">
+        <is>
+          <t>Workplace physical fitness &amp; health insurance underwriting</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C92" s="28" t="inlineStr">
+        <is>
+          <t>Executed Non-Disclosure Agreement (NDA)</t>
+        </is>
+      </c>
+      <c r="D92" s="27" t="inlineStr">
+        <is>
+          <t>docSignedNda</t>
+        </is>
+      </c>
+      <c r="E92" s="27" t="inlineStr">
+        <is>
+          <t>File Upload / Checkbox Agreement</t>
+        </is>
+      </c>
+      <c r="F92" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G92" s="27" t="inlineStr">
+        <is>
+          <t>Indian Contract Act / Trade Secrets Protection</t>
+        </is>
+      </c>
+      <c r="H92" s="27" t="inlineStr">
+        <is>
+          <t>Internal Legal Compliance Hash</t>
+        </is>
+      </c>
+      <c r="I92" s="27" t="inlineStr">
+        <is>
+          <t>PDF / Digital Timestamp</t>
+        </is>
+      </c>
+      <c r="J92" s="27" t="inlineStr">
+        <is>
+          <t>Signed_NDA_IP_Assignment.pdf</t>
+        </is>
+      </c>
+      <c r="K92" s="27" t="inlineStr">
+        <is>
+          <t>Corporate confidentiality &amp; IP assignment execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="23" t="n">
+        <v>89</v>
+      </c>
+      <c r="B93" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C93" s="25" t="inlineStr">
+        <is>
+          <t>Two-Wheeler / Four-Wheeler Field Driving License</t>
+        </is>
+      </c>
+      <c r="D93" s="24" t="inlineStr">
+        <is>
+          <t>docFieldSalesDl</t>
+        </is>
+      </c>
+      <c r="E93" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F93" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G93" s="24" t="inlineStr">
+        <is>
+          <t>Motor Vehicles Act 1988 / Field Travel Policy</t>
+        </is>
+      </c>
+      <c r="H93" s="24" t="inlineStr">
+        <is>
+          <t>CoinCircleTrust MoRTH Sarathi API</t>
+        </is>
+      </c>
+      <c r="I93" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Valid DL)</t>
+        </is>
+      </c>
+      <c r="J93" s="24" t="inlineStr">
+        <is>
+          <t>Driving_License_Field_Sales.pdf</t>
+        </is>
+      </c>
+      <c r="K93" s="24" t="inlineStr">
+        <is>
+          <t>Field client visit authorized vehicle mobility check</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="26" t="n">
+        <v>90</v>
+      </c>
+      <c r="B94" s="27" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C94" s="28" t="inlineStr">
+        <is>
+          <t>Retail Cash Handling &amp; Store POS Policy Agreement</t>
+        </is>
+      </c>
+      <c r="D94" s="27" t="inlineStr">
+        <is>
+          <t>docCashHandlingPolicy</t>
+        </is>
+      </c>
+      <c r="E94" s="27" t="inlineStr">
         <is>
           <t>Checkbox Agreement</t>
         </is>
       </c>
-      <c r="F78" s="9" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="G78" s="10" t="inlineStr">
-        <is>
-          <t>Retail POS &amp; Cash Audit Policy</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>Store Operations Sign-off</t>
-        </is>
-      </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>Boolean (True / False)</t>
-        </is>
-      </c>
-      <c r="J78" s="10" t="inlineStr">
-        <is>
-          <t>True (Acknowledged &amp; Executed)</t>
-        </is>
-      </c>
-      <c r="K78" s="10" t="inlineStr">
-        <is>
-          <t>Liability agreement for POS cash register balancing</t>
+      <c r="F94" s="26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G94" s="27" t="inlineStr">
+        <is>
+          <t>Retail Operations Audit &amp; Loss Prevention Code</t>
+        </is>
+      </c>
+      <c r="H94" s="27" t="inlineStr">
+        <is>
+          <t>Retail Operations Audit Trail</t>
+        </is>
+      </c>
+      <c r="I94" s="27" t="inlineStr">
+        <is>
+          <t>Digital Agreement Checkbox</t>
+        </is>
+      </c>
+      <c r="J94" s="27" t="inlineStr">
+        <is>
+          <t>True (Agreed &amp; Executed)</t>
+        </is>
+      </c>
+      <c r="K94" s="27" t="inlineStr">
+        <is>
+          <t>Cash drawer integrity &amp; POS billing adherence</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="23" t="n">
+        <v>91</v>
+      </c>
+      <c r="B95" s="24" t="inlineStr">
+        <is>
+          <t>11. Document Uploads &amp; Proofs</t>
+        </is>
+      </c>
+      <c r="C95" s="25" t="inlineStr">
+        <is>
+          <t>FSSAI Food Safety &amp; Hygiene Certificate (FoSTaC)</t>
+        </is>
+      </c>
+      <c r="D95" s="24" t="inlineStr">
+        <is>
+          <t>docFssaiFoodCert</t>
+        </is>
+      </c>
+      <c r="E95" s="24" t="inlineStr">
+        <is>
+          <t>File Upload (PDF / Image)</t>
+        </is>
+      </c>
+      <c r="F95" s="23" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="G95" s="24" t="inlineStr">
+        <is>
+          <t>Food Safety &amp; Standards Act 2006 (FSSAI)</t>
+        </is>
+      </c>
+      <c r="H95" s="24" t="inlineStr">
+        <is>
+          <t>FSSAI FoSTaC Training Registry</t>
+        </is>
+      </c>
+      <c r="I95" s="24" t="inlineStr">
+        <is>
+          <t>PDF, JPG (Max 10MB)</t>
+        </is>
+      </c>
+      <c r="J95" s="24" t="inlineStr">
+        <is>
+          <t>FSSAI_FoSTaC_Certificate.pdf</t>
+        </is>
+      </c>
+      <c r="K95" s="24" t="inlineStr">
+        <is>
+          <t>F&amp;B food handling &amp; retail hygiene certification</t>
         </is>
       </c>
     </row>
